--- a/research/traditional_assets/database/data/uruguay/uruguay_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/uruguay/uruguay_restaurant_dining.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1003918292511211</v>
+        <v>0.1001745996779933</v>
       </c>
       <c r="C2">
-        <v>3269.038343576533</v>
+        <v>3246.843477497629</v>
       </c>
       <c r="D2">
-        <v>3153.138343576533</v>
+        <v>3165.735307976166</v>
       </c>
       <c r="E2">
-        <v>-1945.583047853824</v>
+        <v>-1910.791217375286</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34.79183047853824</v>
       </c>
       <c r="G2">
         <v>115.9</v>
@@ -1457,28 +1457,28 @@
         <v>459.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.750029073070474</v>
       </c>
       <c r="N2">
-        <v>459.8</v>
+        <v>458.0499709269295</v>
       </c>
       <c r="O2">
-        <v>114.95</v>
+        <v>114.5124927317324</v>
       </c>
       <c r="P2">
-        <v>344.85</v>
+        <v>343.5374781951971</v>
       </c>
       <c r="Q2">
-        <v>522.05</v>
+        <v>520.7374781951971</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1003918292511211</v>
+        <v>0.1008054037151448</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326222</v>
+        <v>0.850916101658627</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>262.7384922201712</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1001745996779933</v>
+        <v>0.09995737010486555</v>
       </c>
       <c r="C3">
-        <v>3246.843477497629</v>
+        <v>3224.749666296165</v>
       </c>
       <c r="D3">
-        <v>3165.735307976166</v>
+        <v>3178.433327253241</v>
       </c>
       <c r="E3">
-        <v>-1910.791217375286</v>
+        <v>-1875.999386896747</v>
       </c>
       <c r="F3">
-        <v>34.79183047853824</v>
+        <v>69.58366095707649</v>
       </c>
       <c r="G3">
         <v>115.9</v>
@@ -1539,28 +1539,28 @@
         <v>459.8</v>
       </c>
       <c r="M3">
-        <v>1.750029073070474</v>
+        <v>3.500058146140947</v>
       </c>
       <c r="N3">
-        <v>458.0499709269295</v>
+        <v>456.2999418538591</v>
       </c>
       <c r="O3">
-        <v>114.5124927317324</v>
+        <v>114.0749854634648</v>
       </c>
       <c r="P3">
-        <v>343.5374781951971</v>
+        <v>342.2249563903943</v>
       </c>
       <c r="Q3">
-        <v>520.7374781951971</v>
+        <v>519.4249563903943</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1008054037151448</v>
+        <v>0.1012274184743526</v>
       </c>
       <c r="T3">
-        <v>0.850916101658627</v>
+        <v>0.8574445357667951</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>262.7384922201712</v>
+        <v>131.3692461100856</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09995737010486555</v>
+        <v>0.09974014053173771</v>
       </c>
       <c r="C4">
-        <v>3224.749666296165</v>
+        <v>3202.758130887089</v>
       </c>
       <c r="D4">
-        <v>3178.433327253241</v>
+        <v>3191.233622322703</v>
       </c>
       <c r="E4">
-        <v>-1875.999386896747</v>
+        <v>-1841.207556418209</v>
       </c>
       <c r="F4">
-        <v>69.58366095707649</v>
+        <v>104.3754914356147</v>
       </c>
       <c r="G4">
         <v>115.9</v>
@@ -1621,28 +1621,28 @@
         <v>459.8</v>
       </c>
       <c r="M4">
-        <v>3.500058146140947</v>
+        <v>5.25008721921142</v>
       </c>
       <c r="N4">
-        <v>456.2999418538591</v>
+        <v>454.5499127807886</v>
       </c>
       <c r="O4">
-        <v>114.0749854634648</v>
+        <v>113.6374781951971</v>
       </c>
       <c r="P4">
-        <v>342.2249563903943</v>
+        <v>340.9124345855914</v>
       </c>
       <c r="Q4">
-        <v>519.4249563903943</v>
+        <v>518.1124345855915</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1012274184743526</v>
+        <v>0.1016581345688018</v>
       </c>
       <c r="T4">
-        <v>0.8574445357667951</v>
+        <v>0.8641075767637912</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>131.3692461100856</v>
+        <v>87.57949740672373</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09974014053173771</v>
+        <v>0.09952291095860993</v>
       </c>
       <c r="C5">
-        <v>3202.758130887089</v>
+        <v>3180.870111932507</v>
       </c>
       <c r="D5">
-        <v>3191.233622322703</v>
+        <v>3204.13743384666</v>
       </c>
       <c r="E5">
-        <v>-1841.207556418209</v>
+        <v>-1806.415725939671</v>
       </c>
       <c r="F5">
-        <v>104.3754914356147</v>
+        <v>139.167321914153</v>
       </c>
       <c r="G5">
         <v>115.9</v>
@@ -1703,28 +1703,28 @@
         <v>459.8</v>
       </c>
       <c r="M5">
-        <v>5.25008721921142</v>
+        <v>7.000116292281894</v>
       </c>
       <c r="N5">
-        <v>454.5499127807886</v>
+        <v>452.7998837077181</v>
       </c>
       <c r="O5">
-        <v>113.6374781951971</v>
+        <v>113.1999709269295</v>
       </c>
       <c r="P5">
-        <v>340.9124345855914</v>
+        <v>339.5999127807886</v>
       </c>
       <c r="Q5">
-        <v>518.1124345855915</v>
+        <v>516.7999127807886</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1016581345688018</v>
+        <v>0.1020978239152187</v>
       </c>
       <c r="T5">
-        <v>0.8641075767637912</v>
+        <v>0.8709094311148917</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>87.57949740672373</v>
+        <v>65.68462305504279</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09952291095860993</v>
+        <v>0.09930568138548213</v>
       </c>
       <c r="C6">
-        <v>3180.870111932507</v>
+        <v>3159.086870242565</v>
       </c>
       <c r="D6">
-        <v>3204.13743384666</v>
+        <v>3217.146022635256</v>
       </c>
       <c r="E6">
-        <v>-1806.415725939671</v>
+        <v>-1771.623895461133</v>
       </c>
       <c r="F6">
-        <v>139.167321914153</v>
+        <v>173.9591523926912</v>
       </c>
       <c r="G6">
         <v>115.9</v>
@@ -1785,28 +1785,28 @@
         <v>459.8</v>
       </c>
       <c r="M6">
-        <v>7.000116292281894</v>
+        <v>8.750145365352367</v>
       </c>
       <c r="N6">
-        <v>452.7998837077181</v>
+        <v>451.0498546346477</v>
       </c>
       <c r="O6">
-        <v>113.1999709269295</v>
+        <v>112.7624636586619</v>
       </c>
       <c r="P6">
-        <v>339.5999127807886</v>
+        <v>338.2873909759858</v>
       </c>
       <c r="Q6">
-        <v>516.7999127807886</v>
+        <v>515.4873909759858</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1020978239152187</v>
+        <v>0.1025467698794549</v>
       </c>
       <c r="T6">
-        <v>0.8709094311148917</v>
+        <v>0.8778544823996994</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>65.68462305504279</v>
+        <v>52.54769844403425</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09930568138548213</v>
+        <v>0.0990884518123543</v>
       </c>
       <c r="C7">
-        <v>3159.086870242565</v>
+        <v>3137.409687186094</v>
       </c>
       <c r="D7">
-        <v>3217.146022635256</v>
+        <v>3230.260670057324</v>
       </c>
       <c r="E7">
-        <v>-1771.623895461133</v>
+        <v>-1736.832064982594</v>
       </c>
       <c r="F7">
-        <v>173.9591523926912</v>
+        <v>208.7509828712295</v>
       </c>
       <c r="G7">
         <v>115.9</v>
@@ -1867,28 +1867,28 @@
         <v>459.8</v>
       </c>
       <c r="M7">
-        <v>8.750145365352367</v>
+        <v>10.50017443842284</v>
       </c>
       <c r="N7">
-        <v>451.0498546346477</v>
+        <v>449.2998255615772</v>
       </c>
       <c r="O7">
-        <v>112.7624636586619</v>
+        <v>112.3249563903943</v>
       </c>
       <c r="P7">
-        <v>338.2873909759858</v>
+        <v>336.9748691711829</v>
       </c>
       <c r="Q7">
-        <v>515.4873909759858</v>
+        <v>514.1748691711829</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1025467698794549</v>
+        <v>0.1030052678854833</v>
       </c>
       <c r="T7">
-        <v>0.8778544823996994</v>
+        <v>0.8849473007331201</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>52.54769844403425</v>
+        <v>43.78974870336186</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0990884518123543</v>
+        <v>0.09887122223922652</v>
       </c>
       <c r="C8">
-        <v>3137.409687186094</v>
+        <v>3115.839865111376</v>
       </c>
       <c r="D8">
-        <v>3230.260670057324</v>
+        <v>3243.482678461143</v>
       </c>
       <c r="E8">
-        <v>-1736.832064982595</v>
+        <v>-1702.040234504056</v>
       </c>
       <c r="F8">
-        <v>208.7509828712294</v>
+        <v>243.5428133497677</v>
       </c>
       <c r="G8">
         <v>115.9</v>
@@ -1949,28 +1949,28 @@
         <v>459.8</v>
       </c>
       <c r="M8">
-        <v>10.50017443842284</v>
+        <v>12.25020351149331</v>
       </c>
       <c r="N8">
-        <v>449.2998255615772</v>
+        <v>447.5497964885067</v>
       </c>
       <c r="O8">
-        <v>112.3249563903943</v>
+        <v>111.8874491221267</v>
       </c>
       <c r="P8">
-        <v>336.9748691711829</v>
+        <v>335.66234736638</v>
       </c>
       <c r="Q8">
-        <v>514.1748691711829</v>
+        <v>512.8623473663799</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1030052678854833</v>
+        <v>0.1034736260636844</v>
       </c>
       <c r="T8">
-        <v>0.8849473007331201</v>
+        <v>0.8921926527941412</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>43.78974870336187</v>
+        <v>37.53407031716732</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09887122223922651</v>
+        <v>0.09865399266609873</v>
       </c>
       <c r="C9">
-        <v>3115.839865111377</v>
+        <v>3094.378727777264</v>
       </c>
       <c r="D9">
-        <v>3243.482678461144</v>
+        <v>3256.81337160557</v>
       </c>
       <c r="E9">
-        <v>-1702.040234504056</v>
+        <v>-1667.248404025518</v>
       </c>
       <c r="F9">
-        <v>243.5428133497677</v>
+        <v>278.334643828306</v>
       </c>
       <c r="G9">
         <v>115.9</v>
@@ -2031,28 +2031,28 @@
         <v>459.8</v>
       </c>
       <c r="M9">
-        <v>12.25020351149331</v>
+        <v>14.00023258456379</v>
       </c>
       <c r="N9">
-        <v>447.5497964885067</v>
+        <v>445.7997674154362</v>
       </c>
       <c r="O9">
-        <v>111.8874491221267</v>
+        <v>111.4499418538591</v>
       </c>
       <c r="P9">
-        <v>335.66234736638</v>
+        <v>334.3498255615772</v>
       </c>
       <c r="Q9">
-        <v>512.8623473663799</v>
+        <v>511.5498255615772</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1034736260636844</v>
+        <v>0.1039521659414117</v>
       </c>
       <c r="T9">
-        <v>0.8921926527941412</v>
+        <v>0.8995955125086629</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.53407031716731</v>
+        <v>32.8423115275214</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09865399266609873</v>
+        <v>0.09843676309297092</v>
       </c>
       <c r="C10">
-        <v>3094.378727777264</v>
+        <v>3073.027620794986</v>
       </c>
       <c r="D10">
-        <v>3256.81337160557</v>
+        <v>3270.25409510183</v>
       </c>
       <c r="E10">
-        <v>-1667.248404025518</v>
+        <v>-1632.45657354698</v>
       </c>
       <c r="F10">
-        <v>278.334643828306</v>
+        <v>313.1264743068442</v>
       </c>
       <c r="G10">
         <v>115.9</v>
@@ -2113,28 +2113,28 @@
         <v>459.8</v>
       </c>
       <c r="M10">
-        <v>14.00023258456379</v>
+        <v>15.75026165763426</v>
       </c>
       <c r="N10">
-        <v>445.7997674154362</v>
+        <v>444.0497383423657</v>
       </c>
       <c r="O10">
-        <v>111.4499418538591</v>
+        <v>111.0124345855914</v>
       </c>
       <c r="P10">
-        <v>334.3498255615772</v>
+        <v>333.0373037567743</v>
       </c>
       <c r="Q10">
-        <v>511.5498255615772</v>
+        <v>510.2373037567743</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1039521659414117</v>
+        <v>0.1044412231790889</v>
       </c>
       <c r="T10">
-        <v>0.8995955125086629</v>
+        <v>0.9071610724366903</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.8423115275214</v>
+        <v>29.19316580224125</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09843676309297092</v>
+        <v>0.0982195335198431</v>
       </c>
       <c r="C11">
-        <v>3073.027620794986</v>
+        <v>3051.787912080935</v>
       </c>
       <c r="D11">
-        <v>3270.25409510183</v>
+        <v>3283.806216866317</v>
       </c>
       <c r="E11">
-        <v>-1632.45657354698</v>
+        <v>-1597.664743068442</v>
       </c>
       <c r="F11">
-        <v>313.1264743068442</v>
+        <v>347.9183047853824</v>
       </c>
       <c r="G11">
         <v>115.9</v>
@@ -2195,28 +2195,28 @@
         <v>459.8</v>
       </c>
       <c r="M11">
-        <v>15.75026165763426</v>
+        <v>17.50029073070473</v>
       </c>
       <c r="N11">
-        <v>444.0497383423657</v>
+        <v>442.2997092692953</v>
       </c>
       <c r="O11">
-        <v>111.0124345855914</v>
+        <v>110.5749273173238</v>
       </c>
       <c r="P11">
-        <v>333.0373037567743</v>
+        <v>331.7247819519715</v>
       </c>
       <c r="Q11">
-        <v>510.2373037567743</v>
+        <v>508.9247819519715</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1044412231790889</v>
+        <v>0.1049411483553812</v>
       </c>
       <c r="T11">
-        <v>0.9071610724366903</v>
+        <v>0.914894755918674</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.19316580224125</v>
+        <v>26.27384922201713</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0982195335198431</v>
+        <v>0.0980023039467153</v>
       </c>
       <c r="C12">
-        <v>3051.787912080934</v>
+        <v>3030.660992320751</v>
       </c>
       <c r="D12">
-        <v>3283.806216866317</v>
+        <v>3297.471127584671</v>
       </c>
       <c r="E12">
-        <v>-1597.664743068442</v>
+        <v>-1562.872912589903</v>
       </c>
       <c r="F12">
-        <v>347.9183047853824</v>
+        <v>382.7101352639207</v>
       </c>
       <c r="G12">
         <v>115.9</v>
@@ -2277,28 +2277,28 @@
         <v>459.8</v>
       </c>
       <c r="M12">
-        <v>17.50029073070473</v>
+        <v>19.25031980377521</v>
       </c>
       <c r="N12">
-        <v>442.2997092692952</v>
+        <v>440.5496801962248</v>
       </c>
       <c r="O12">
-        <v>110.5749273173238</v>
+        <v>110.1374200490562</v>
       </c>
       <c r="P12">
-        <v>331.7247819519714</v>
+        <v>330.4122601471686</v>
       </c>
       <c r="Q12">
-        <v>508.9247819519714</v>
+        <v>507.6122601471686</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1049411483553812</v>
+        <v>0.1054523078052981</v>
       </c>
       <c r="T12">
-        <v>0.914894755918674</v>
+        <v>0.9228022300407024</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.27384922201712</v>
+        <v>23.88531747456102</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0980023039467153</v>
+        <v>0.09778507437358751</v>
       </c>
       <c r="C13">
-        <v>3030.660992320751</v>
+        <v>3009.648275445065</v>
       </c>
       <c r="D13">
-        <v>3297.471127584671</v>
+        <v>3311.250241187524</v>
       </c>
       <c r="E13">
-        <v>-1562.872912589903</v>
+        <v>-1528.081082111365</v>
       </c>
       <c r="F13">
-        <v>382.7101352639207</v>
+        <v>417.5019657424589</v>
       </c>
       <c r="G13">
         <v>115.9</v>
@@ -2359,28 +2359,28 @@
         <v>459.8</v>
       </c>
       <c r="M13">
-        <v>19.25031980377521</v>
+        <v>21.00034887684568</v>
       </c>
       <c r="N13">
-        <v>440.5496801962248</v>
+        <v>438.7996511231543</v>
       </c>
       <c r="O13">
-        <v>110.1374200490562</v>
+        <v>109.6999127807886</v>
       </c>
       <c r="P13">
-        <v>330.4122601471686</v>
+        <v>329.0997383423658</v>
       </c>
       <c r="Q13">
-        <v>507.6122601471686</v>
+        <v>506.2997383423657</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1054523078052981</v>
+        <v>0.1059750845154403</v>
       </c>
       <c r="T13">
-        <v>0.9228022300407024</v>
+        <v>0.9308894194836859</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.88531747456102</v>
+        <v>21.89487435168093</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09778507437358751</v>
+        <v>0.0975678448004597</v>
       </c>
       <c r="C14">
-        <v>3009.648275445065</v>
+        <v>2988.751199117199</v>
       </c>
       <c r="D14">
-        <v>3311.250241187524</v>
+        <v>3325.144995338196</v>
       </c>
       <c r="E14">
-        <v>-1528.081082111365</v>
+        <v>-1493.289251632827</v>
       </c>
       <c r="F14">
-        <v>417.5019657424589</v>
+        <v>452.2937962209971</v>
       </c>
       <c r="G14">
         <v>115.9</v>
@@ -2441,28 +2441,28 @@
         <v>459.8</v>
       </c>
       <c r="M14">
-        <v>21.00034887684568</v>
+        <v>22.75037794991615</v>
       </c>
       <c r="N14">
-        <v>438.7996511231543</v>
+        <v>437.0496220500839</v>
       </c>
       <c r="O14">
-        <v>109.6999127807886</v>
+        <v>109.262405512521</v>
       </c>
       <c r="P14">
-        <v>329.0997383423658</v>
+        <v>327.7872165375629</v>
       </c>
       <c r="Q14">
-        <v>506.2997383423657</v>
+        <v>504.9872165375629</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1059750845154403</v>
+        <v>0.1065098790809882</v>
       </c>
       <c r="T14">
-        <v>0.9308894194836859</v>
+        <v>0.9391625213276574</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.89487435168093</v>
+        <v>20.21065324770548</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0975678448004597</v>
+        <v>0.09735061522733189</v>
       </c>
       <c r="C15">
-        <v>2988.751199117199</v>
+        <v>2967.971225233195</v>
       </c>
       <c r="D15">
-        <v>3325.144995338196</v>
+        <v>3339.15685193273</v>
       </c>
       <c r="E15">
-        <v>-1493.289251632827</v>
+        <v>-1458.497421154289</v>
       </c>
       <c r="F15">
-        <v>452.2937962209971</v>
+        <v>487.0856266995354</v>
       </c>
       <c r="G15">
         <v>115.9</v>
@@ -2523,28 +2523,28 @@
         <v>459.8</v>
       </c>
       <c r="M15">
-        <v>22.75037794991615</v>
+        <v>24.50040702298663</v>
       </c>
       <c r="N15">
-        <v>437.0496220500839</v>
+        <v>435.2995929770134</v>
       </c>
       <c r="O15">
-        <v>109.262405512521</v>
+        <v>108.8248982442533</v>
       </c>
       <c r="P15">
-        <v>327.7872165375629</v>
+        <v>326.47469473276</v>
       </c>
       <c r="Q15">
-        <v>504.9872165375629</v>
+        <v>503.67469473276</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1065098790809882</v>
+        <v>0.1070571107294557</v>
       </c>
       <c r="T15">
-        <v>0.9391625213276574</v>
+        <v>0.9476280208889307</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.21065324770548</v>
+        <v>18.76703515858366</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09735061522733189</v>
+        <v>0.0971333856542041</v>
       </c>
       <c r="C16">
-        <v>2967.971225233195</v>
+        <v>2947.309840434557</v>
       </c>
       <c r="D16">
-        <v>3339.15685193273</v>
+        <v>3353.28729761263</v>
       </c>
       <c r="E16">
-        <v>-1458.497421154289</v>
+        <v>-1423.70559067575</v>
       </c>
       <c r="F16">
-        <v>487.0856266995354</v>
+        <v>521.8774571780737</v>
       </c>
       <c r="G16">
         <v>115.9</v>
@@ -2605,28 +2605,28 @@
         <v>459.8</v>
       </c>
       <c r="M16">
-        <v>24.50040702298663</v>
+        <v>26.2504360960571</v>
       </c>
       <c r="N16">
-        <v>435.2995929770134</v>
+        <v>433.5495639039429</v>
       </c>
       <c r="O16">
-        <v>108.8248982442533</v>
+        <v>108.3873909759857</v>
       </c>
       <c r="P16">
-        <v>326.47469473276</v>
+        <v>325.1621729279572</v>
       </c>
       <c r="Q16">
-        <v>503.67469473276</v>
+        <v>502.3621729279571</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1070571107294557</v>
+        <v>0.1076172184167107</v>
       </c>
       <c r="T16">
-        <v>0.9476280208889307</v>
+        <v>0.9562927086751751</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.76703515858366</v>
+        <v>17.51589948134475</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0971333856542041</v>
+        <v>0.09691615608107629</v>
       </c>
       <c r="C17">
-        <v>2947.309840434557</v>
+        <v>2926.768556634058</v>
       </c>
       <c r="D17">
-        <v>3353.28729761263</v>
+        <v>3367.537844290669</v>
       </c>
       <c r="E17">
-        <v>-1423.70559067575</v>
+        <v>-1388.913760197212</v>
       </c>
       <c r="F17">
-        <v>521.8774571780735</v>
+        <v>556.6692876566119</v>
       </c>
       <c r="G17">
         <v>115.9</v>
@@ -2687,28 +2687,28 @@
         <v>459.8</v>
       </c>
       <c r="M17">
-        <v>26.2504360960571</v>
+        <v>28.00046516912758</v>
       </c>
       <c r="N17">
-        <v>433.5495639039429</v>
+        <v>431.7995348308725</v>
       </c>
       <c r="O17">
-        <v>108.3873909759857</v>
+        <v>107.9498837077181</v>
       </c>
       <c r="P17">
-        <v>325.1621729279572</v>
+        <v>323.8496511231543</v>
       </c>
       <c r="Q17">
-        <v>502.3621729279571</v>
+        <v>501.0496511231543</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1076172184167107</v>
+        <v>0.1081906620012813</v>
       </c>
       <c r="T17">
-        <v>0.9562927086751751</v>
+        <v>0.9651636985515682</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.51589948134475</v>
+        <v>16.4211557637607</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09691615608107629</v>
+        <v>0.09669892650794848</v>
       </c>
       <c r="C18">
-        <v>2926.768556634058</v>
+        <v>2906.348911555004</v>
       </c>
       <c r="D18">
-        <v>3367.537844290669</v>
+        <v>3381.910029690154</v>
       </c>
       <c r="E18">
-        <v>-1388.913760197212</v>
+        <v>-1354.121929718674</v>
       </c>
       <c r="F18">
-        <v>556.6692876566119</v>
+        <v>591.4611181351502</v>
       </c>
       <c r="G18">
         <v>115.9</v>
@@ -2769,28 +2769,28 @@
         <v>459.8</v>
       </c>
       <c r="M18">
-        <v>28.00046516912758</v>
+        <v>29.75049424219805</v>
       </c>
       <c r="N18">
-        <v>431.7995348308725</v>
+        <v>430.049505757802</v>
       </c>
       <c r="O18">
-        <v>107.9498837077181</v>
+        <v>107.5123764394505</v>
       </c>
       <c r="P18">
-        <v>323.8496511231543</v>
+        <v>322.5371293183515</v>
       </c>
       <c r="Q18">
-        <v>501.0496511231543</v>
+        <v>499.7371293183515</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1081906620012813</v>
+        <v>0.1087779235035524</v>
       </c>
       <c r="T18">
-        <v>0.9651636985515682</v>
+        <v>0.9742484472201637</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.4211557637607</v>
+        <v>15.45520542471595</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09669892650794848</v>
+        <v>0.09648169693482068</v>
       </c>
       <c r="C19">
-        <v>2906.348911555004</v>
+        <v>2886.052469284383</v>
       </c>
       <c r="D19">
-        <v>3381.910029690154</v>
+        <v>3396.405417898071</v>
       </c>
       <c r="E19">
-        <v>-1354.121929718674</v>
+        <v>-1319.330099240135</v>
       </c>
       <c r="F19">
-        <v>591.4611181351502</v>
+        <v>626.2529486136884</v>
       </c>
       <c r="G19">
         <v>115.9</v>
@@ -2851,28 +2851,28 @@
         <v>459.8</v>
       </c>
       <c r="M19">
-        <v>29.75049424219805</v>
+        <v>31.50052331526853</v>
       </c>
       <c r="N19">
-        <v>430.049505757802</v>
+        <v>428.2994766847315</v>
       </c>
       <c r="O19">
-        <v>107.5123764394505</v>
+        <v>107.0748691711829</v>
       </c>
       <c r="P19">
-        <v>322.5371293183515</v>
+        <v>321.2246075135486</v>
       </c>
       <c r="Q19">
-        <v>499.7371293183515</v>
+        <v>498.4246075135486</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1087779235035524</v>
+        <v>0.1093795084570984</v>
       </c>
       <c r="T19">
-        <v>0.9742484472201637</v>
+        <v>0.9835547751245782</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.45520542471595</v>
+        <v>14.59658290112062</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0964816969348207</v>
+        <v>0.09626446736169289</v>
       </c>
       <c r="C20">
-        <v>2886.052469284382</v>
+        <v>2865.880820840282</v>
       </c>
       <c r="D20">
-        <v>3396.40541789807</v>
+        <v>3411.025599932509</v>
       </c>
       <c r="E20">
-        <v>-1319.330099240135</v>
+        <v>-1284.538268761597</v>
       </c>
       <c r="F20">
-        <v>626.2529486136883</v>
+        <v>661.0447790922266</v>
       </c>
       <c r="G20">
         <v>115.9</v>
@@ -2933,28 +2933,28 @@
         <v>459.8</v>
       </c>
       <c r="M20">
-        <v>31.50052331526852</v>
+        <v>33.250552388339</v>
       </c>
       <c r="N20">
-        <v>428.2994766847315</v>
+        <v>426.549447611661</v>
       </c>
       <c r="O20">
-        <v>107.0748691711829</v>
+        <v>106.6373619029153</v>
       </c>
       <c r="P20">
-        <v>321.2246075135486</v>
+        <v>319.9120857087458</v>
       </c>
       <c r="Q20">
-        <v>498.4246075135486</v>
+        <v>497.1120857087458</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1093795084570984</v>
+        <v>0.1099959473601147</v>
       </c>
       <c r="T20">
-        <v>0.9835547751245782</v>
+        <v>0.9930908889031762</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.59658290112062</v>
+        <v>13.82834169579849</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09626446736169289</v>
+        <v>0.09604723778856508</v>
       </c>
       <c r="C21">
-        <v>2865.880820840282</v>
+        <v>2845.835584754043</v>
       </c>
       <c r="D21">
-        <v>3411.025599932509</v>
+        <v>3425.772194324808</v>
       </c>
       <c r="E21">
-        <v>-1284.538268761597</v>
+        <v>-1249.746438283059</v>
       </c>
       <c r="F21">
-        <v>661.0447790922266</v>
+        <v>695.8366095707648</v>
       </c>
       <c r="G21">
         <v>115.9</v>
@@ -3015,28 +3015,28 @@
         <v>459.8</v>
       </c>
       <c r="M21">
-        <v>33.250552388339</v>
+        <v>35.00058146140947</v>
       </c>
       <c r="N21">
-        <v>426.549447611661</v>
+        <v>424.7994185385905</v>
       </c>
       <c r="O21">
-        <v>106.6373619029153</v>
+        <v>106.1998546346476</v>
       </c>
       <c r="P21">
-        <v>319.9120857087458</v>
+        <v>318.5995639039429</v>
       </c>
       <c r="Q21">
-        <v>497.1120857087458</v>
+        <v>495.7995639039429</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1099959473601147</v>
+        <v>0.1106277972357063</v>
       </c>
       <c r="T21">
-        <v>0.9930908889031762</v>
+        <v>1.002865405526239</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.82834169579849</v>
+        <v>13.13692461100856</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09604723778856508</v>
+        <v>0.09606625821543728</v>
       </c>
       <c r="C22">
-        <v>2845.835584754043</v>
+        <v>2809.747464242861</v>
       </c>
       <c r="D22">
-        <v>3425.772194324808</v>
+        <v>3424.475904292165</v>
       </c>
       <c r="E22">
-        <v>-1249.746438283059</v>
+        <v>-1214.954607804521</v>
       </c>
       <c r="F22">
-        <v>695.8366095707648</v>
+        <v>730.6284400493031</v>
       </c>
       <c r="G22">
         <v>115.9</v>
@@ -3097,45 +3097,45 @@
         <v>459.8</v>
       </c>
       <c r="M22">
-        <v>35.00058146140947</v>
+        <v>37.8465531945539</v>
       </c>
       <c r="N22">
-        <v>424.7994185385905</v>
+        <v>421.9534468054461</v>
       </c>
       <c r="O22">
-        <v>106.1998546346476</v>
+        <v>105.4883617013615</v>
       </c>
       <c r="P22">
-        <v>318.5995639039429</v>
+        <v>316.4650851040846</v>
       </c>
       <c r="Q22">
-        <v>495.7995639039429</v>
+        <v>493.6650851040845</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1106277972357063</v>
+        <v>0.1112756433106801</v>
       </c>
       <c r="T22">
-        <v>1.002865405526239</v>
+        <v>1.012887378266341</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.13692461100856</v>
+        <v>12.14905879635467</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09606625821543728</v>
+        <v>0.09586027864230948</v>
       </c>
       <c r="C23">
-        <v>2809.747464242861</v>
+        <v>2789.046088393883</v>
       </c>
       <c r="D23">
-        <v>3424.475904292165</v>
+        <v>3438.566358921724</v>
       </c>
       <c r="E23">
-        <v>-1214.954607804521</v>
+        <v>-1180.162777325982</v>
       </c>
       <c r="F23">
-        <v>730.628440049303</v>
+        <v>765.4202705278414</v>
       </c>
       <c r="G23">
         <v>115.9</v>
@@ -3179,28 +3179,28 @@
         <v>459.8</v>
       </c>
       <c r="M23">
-        <v>37.84655319455389</v>
+        <v>39.64877001334218</v>
       </c>
       <c r="N23">
-        <v>421.9534468054461</v>
+        <v>420.1512299866578</v>
       </c>
       <c r="O23">
-        <v>105.4883617013615</v>
+        <v>105.0378074966645</v>
       </c>
       <c r="P23">
-        <v>316.4650851040846</v>
+        <v>315.1134224899934</v>
       </c>
       <c r="Q23">
-        <v>493.6650851040845</v>
+        <v>492.3134224899933</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1112756433106801</v>
+        <v>0.1119401008234737</v>
       </c>
       <c r="T23">
-        <v>1.012887378266341</v>
+        <v>1.023166324666446</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.14905879635467</v>
+        <v>11.59682885106582</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09586027864230948</v>
+        <v>0.09565429906918169</v>
       </c>
       <c r="C24">
-        <v>2789.046088393883</v>
+        <v>2768.461145666377</v>
       </c>
       <c r="D24">
-        <v>3438.566358921724</v>
+        <v>3452.773246672757</v>
       </c>
       <c r="E24">
-        <v>-1180.162777325982</v>
+        <v>-1145.370946847444</v>
       </c>
       <c r="F24">
-        <v>765.4202705278414</v>
+        <v>800.2121010063796</v>
       </c>
       <c r="G24">
         <v>115.9</v>
@@ -3261,28 +3261,28 @@
         <v>459.8</v>
       </c>
       <c r="M24">
-        <v>39.64877001334218</v>
+        <v>41.45098683213046</v>
       </c>
       <c r="N24">
-        <v>420.1512299866578</v>
+        <v>418.3490131678695</v>
       </c>
       <c r="O24">
-        <v>105.0378074966645</v>
+        <v>104.5872532919674</v>
       </c>
       <c r="P24">
-        <v>315.1134224899934</v>
+        <v>313.7617598759022</v>
       </c>
       <c r="Q24">
-        <v>492.3134224899933</v>
+        <v>490.9617598759021</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1119401008234737</v>
+        <v>0.1126218169729632</v>
       </c>
       <c r="T24">
-        <v>1.023166324666446</v>
+        <v>1.033712256687333</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.59682885106582</v>
+        <v>11.09261890101948</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09565429906918169</v>
+        <v>0.09544831949605388</v>
       </c>
       <c r="C25">
-        <v>2768.461145666377</v>
+        <v>2747.994085223878</v>
       </c>
       <c r="D25">
-        <v>3452.773246672757</v>
+        <v>3467.098016708796</v>
       </c>
       <c r="E25">
-        <v>-1145.370946847444</v>
+        <v>-1110.579116368906</v>
       </c>
       <c r="F25">
-        <v>800.2121010063796</v>
+        <v>835.0039314849179</v>
       </c>
       <c r="G25">
         <v>115.9</v>
@@ -3343,28 +3343,28 @@
         <v>459.8</v>
       </c>
       <c r="M25">
-        <v>41.45098683213046</v>
+        <v>43.25320365091874</v>
       </c>
       <c r="N25">
-        <v>418.3490131678695</v>
+        <v>416.5467963490813</v>
       </c>
       <c r="O25">
-        <v>104.5872532919674</v>
+        <v>104.1366990872703</v>
       </c>
       <c r="P25">
-        <v>313.7617598759022</v>
+        <v>312.410097261811</v>
       </c>
       <c r="Q25">
-        <v>490.9617598759021</v>
+        <v>489.6100972618109</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1126218169729632</v>
+        <v>0.1133214730211235</v>
       </c>
       <c r="T25">
-        <v>1.033712256687333</v>
+        <v>1.044535713235085</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.09261890101948</v>
+        <v>10.63042644681034</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09544831949605388</v>
+        <v>0.09524233992292605</v>
       </c>
       <c r="C26">
-        <v>2747.994085223878</v>
+        <v>2727.646380379104</v>
       </c>
       <c r="D26">
-        <v>3467.098016708796</v>
+        <v>3481.54214234256</v>
       </c>
       <c r="E26">
-        <v>-1110.579116368906</v>
+        <v>-1075.787285890368</v>
       </c>
       <c r="F26">
-        <v>835.0039314849178</v>
+        <v>869.795761963456</v>
       </c>
       <c r="G26">
         <v>115.9</v>
@@ -3425,28 +3425,28 @@
         <v>459.8</v>
       </c>
       <c r="M26">
-        <v>43.25320365091874</v>
+        <v>45.05542046970702</v>
       </c>
       <c r="N26">
-        <v>416.5467963490813</v>
+        <v>414.744579530293</v>
       </c>
       <c r="O26">
-        <v>104.1366990872703</v>
+        <v>103.6861448825732</v>
       </c>
       <c r="P26">
-        <v>312.410097261811</v>
+        <v>311.0584346477198</v>
       </c>
       <c r="Q26">
-        <v>489.6100972618109</v>
+        <v>488.2584346477198</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1133214730211235</v>
+        <v>0.1140397865639014</v>
       </c>
       <c r="T26">
-        <v>1.044535713235085</v>
+        <v>1.055647795290778</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.63042644681034</v>
+        <v>10.20520938893792</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09524233992292605</v>
+        <v>0.09503636034979825</v>
       </c>
       <c r="C27">
-        <v>2727.646380379104</v>
+        <v>2707.419529099096</v>
       </c>
       <c r="D27">
-        <v>3481.54214234256</v>
+        <v>3496.10712154109</v>
       </c>
       <c r="E27">
-        <v>-1075.787285890368</v>
+        <v>-1040.99545541183</v>
       </c>
       <c r="F27">
-        <v>869.795761963456</v>
+        <v>904.5875924419943</v>
       </c>
       <c r="G27">
         <v>115.9</v>
@@ -3507,28 +3507,28 @@
         <v>459.8</v>
       </c>
       <c r="M27">
-        <v>45.05542046970702</v>
+        <v>46.8576372884953</v>
       </c>
       <c r="N27">
-        <v>414.744579530293</v>
+        <v>412.9423627115047</v>
       </c>
       <c r="O27">
-        <v>103.6861448825732</v>
+        <v>103.2355906778762</v>
       </c>
       <c r="P27">
-        <v>311.0584346477198</v>
+        <v>309.7067720336285</v>
       </c>
       <c r="Q27">
-        <v>488.2584346477198</v>
+        <v>486.9067720336285</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1140397865639014</v>
+        <v>0.1147775139862139</v>
       </c>
       <c r="T27">
-        <v>1.055647795290778</v>
+        <v>1.067060203888516</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.20520938893792</v>
+        <v>9.812701335517234</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09503636034979825</v>
+        <v>0.09517463077667047</v>
       </c>
       <c r="C28">
-        <v>2707.419529099096</v>
+        <v>2662.837079096272</v>
       </c>
       <c r="D28">
-        <v>3496.10712154109</v>
+        <v>3486.316502016804</v>
       </c>
       <c r="E28">
-        <v>-1040.99545541183</v>
+        <v>-1006.203624933291</v>
       </c>
       <c r="F28">
-        <v>904.5875924419943</v>
+        <v>939.3794229205325</v>
       </c>
       <c r="G28">
         <v>115.9</v>
@@ -3589,45 +3589,45 @@
         <v>459.8</v>
       </c>
       <c r="M28">
-        <v>46.8576372884953</v>
+        <v>50.25679912624849</v>
       </c>
       <c r="N28">
-        <v>412.9423627115047</v>
+        <v>409.5432008737515</v>
       </c>
       <c r="O28">
-        <v>103.2355906778762</v>
+        <v>102.3858002184379</v>
       </c>
       <c r="P28">
-        <v>309.7067720336285</v>
+        <v>307.1574006553136</v>
       </c>
       <c r="Q28">
-        <v>486.9067720336285</v>
+        <v>484.3574006553136</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1147775139862139</v>
+        <v>0.1155354531187267</v>
       </c>
       <c r="T28">
-        <v>1.067060203888516</v>
+        <v>1.078785281214959</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>9.812701335517234</v>
+        <v>9.149010840203953</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09517463077667047</v>
+        <v>0.09498140120354268</v>
       </c>
       <c r="C29">
-        <v>2662.837079096272</v>
+        <v>2641.742691817554</v>
       </c>
       <c r="D29">
-        <v>3486.316502016804</v>
+        <v>3500.013945216625</v>
       </c>
       <c r="E29">
-        <v>-1006.203624933291</v>
+        <v>-971.4117944547531</v>
       </c>
       <c r="F29">
-        <v>939.3794229205325</v>
+        <v>974.1712533990708</v>
       </c>
       <c r="G29">
         <v>115.9</v>
@@ -3671,28 +3671,28 @@
         <v>459.8</v>
       </c>
       <c r="M29">
-        <v>50.25679912624849</v>
+        <v>52.11816205685029</v>
       </c>
       <c r="N29">
-        <v>409.5432008737515</v>
+        <v>407.6818379431497</v>
       </c>
       <c r="O29">
-        <v>102.3858002184379</v>
+        <v>101.9204594857874</v>
       </c>
       <c r="P29">
-        <v>307.1574006553136</v>
+        <v>305.7613784573623</v>
       </c>
       <c r="Q29">
-        <v>484.3574006553136</v>
+        <v>482.9613784573623</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1155354531187267</v>
+        <v>0.1163144461160315</v>
       </c>
       <c r="T29">
-        <v>1.078785281214959</v>
+        <v>1.090836055133804</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.149010840203953</v>
+        <v>8.822260453053811</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09498140120354268</v>
+        <v>0.09478817163041486</v>
       </c>
       <c r="C30">
-        <v>2641.742691817554</v>
+        <v>2620.756361280469</v>
       </c>
       <c r="D30">
-        <v>3500.013945216625</v>
+        <v>3513.819445158078</v>
       </c>
       <c r="E30">
-        <v>-971.4117944547531</v>
+        <v>-936.6199639762149</v>
       </c>
       <c r="F30">
-        <v>974.1712533990708</v>
+        <v>1008.963083877609</v>
       </c>
       <c r="G30">
         <v>115.9</v>
@@ -3753,28 +3753,28 @@
         <v>459.8</v>
       </c>
       <c r="M30">
-        <v>52.11816205685029</v>
+        <v>53.97952498745208</v>
       </c>
       <c r="N30">
-        <v>407.6818379431497</v>
+        <v>405.8204750125479</v>
       </c>
       <c r="O30">
-        <v>101.9204594857874</v>
+        <v>101.455118753137</v>
       </c>
       <c r="P30">
-        <v>305.7613784573623</v>
+        <v>304.365356259411</v>
       </c>
       <c r="Q30">
-        <v>482.9613784573623</v>
+        <v>481.565356259411</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1163144461160315</v>
+        <v>0.1171153825780491</v>
       </c>
       <c r="T30">
-        <v>1.090836055133804</v>
+        <v>1.103226287472897</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.822260453053811</v>
+        <v>8.518044575362302</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09478817163041486</v>
+        <v>0.09459494205728705</v>
       </c>
       <c r="C31">
-        <v>2620.756361280469</v>
+        <v>2599.879371209753</v>
       </c>
       <c r="D31">
-        <v>3513.819445158078</v>
+        <v>3527.7342855659</v>
       </c>
       <c r="E31">
-        <v>-936.619963976215</v>
+        <v>-901.8281334976768</v>
       </c>
       <c r="F31">
-        <v>1008.963083877609</v>
+        <v>1043.754914356147</v>
       </c>
       <c r="G31">
         <v>115.9</v>
@@ -3835,28 +3835,28 @@
         <v>459.8</v>
       </c>
       <c r="M31">
-        <v>53.97952498745208</v>
+        <v>55.84088791805387</v>
       </c>
       <c r="N31">
-        <v>405.8204750125479</v>
+        <v>403.9591120819462</v>
       </c>
       <c r="O31">
-        <v>101.455118753137</v>
+        <v>100.9897780204865</v>
       </c>
       <c r="P31">
-        <v>304.365356259411</v>
+        <v>302.9693340614596</v>
       </c>
       <c r="Q31">
-        <v>481.565356259411</v>
+        <v>480.1693340614596</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1171153825780491</v>
+        <v>0.1179392029389815</v>
       </c>
       <c r="T31">
-        <v>1.103226287472897</v>
+        <v>1.115970526450251</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.518044575362302</v>
+        <v>8.23410975618356</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09459494205728705</v>
+        <v>0.09440171248415923</v>
       </c>
       <c r="C32">
-        <v>2599.879371209753</v>
+        <v>2579.113025745359</v>
       </c>
       <c r="D32">
-        <v>3527.7342855659</v>
+        <v>3541.759770580044</v>
       </c>
       <c r="E32">
-        <v>-901.8281334976768</v>
+        <v>-867.0363030191386</v>
       </c>
       <c r="F32">
-        <v>1043.754914356147</v>
+        <v>1078.546744834685</v>
       </c>
       <c r="G32">
         <v>115.9</v>
@@ -3917,28 +3917,28 @@
         <v>459.8</v>
       </c>
       <c r="M32">
-        <v>55.84088791805387</v>
+        <v>57.70225084865567</v>
       </c>
       <c r="N32">
-        <v>403.9591120819462</v>
+        <v>402.0977491513444</v>
       </c>
       <c r="O32">
-        <v>100.9897780204865</v>
+        <v>100.5244372878361</v>
       </c>
       <c r="P32">
-        <v>302.9693340614596</v>
+        <v>301.5733118635083</v>
       </c>
       <c r="Q32">
-        <v>480.1693340614596</v>
+        <v>478.7733118635082</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1179392029389815</v>
+        <v>0.1187869021509554</v>
       </c>
       <c r="T32">
-        <v>1.115970526450251</v>
+        <v>1.129084163658832</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.23410975618356</v>
+        <v>7.968493312435703</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09440171248415923</v>
+        <v>0.09420848291103144</v>
       </c>
       <c r="C33">
-        <v>2579.113025745359</v>
+        <v>2558.458649849897</v>
       </c>
       <c r="D33">
-        <v>3541.759770580044</v>
+        <v>3555.89722516312</v>
       </c>
       <c r="E33">
-        <v>-867.0363030191386</v>
+        <v>-832.2444725406001</v>
       </c>
       <c r="F33">
-        <v>1078.546744834685</v>
+        <v>1113.338575313224</v>
       </c>
       <c r="G33">
         <v>115.9</v>
@@ -3999,28 +3999,28 @@
         <v>459.8</v>
       </c>
       <c r="M33">
-        <v>57.70225084865567</v>
+        <v>59.56361377925747</v>
       </c>
       <c r="N33">
-        <v>402.0977491513444</v>
+        <v>400.2363862207425</v>
       </c>
       <c r="O33">
-        <v>100.5244372878361</v>
+        <v>100.0590965551856</v>
       </c>
       <c r="P33">
-        <v>301.5733118635083</v>
+        <v>300.1772896655569</v>
       </c>
       <c r="Q33">
-        <v>478.7733118635082</v>
+        <v>477.3772896655569</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1187869021509554</v>
+        <v>0.1196595336926933</v>
       </c>
       <c r="T33">
-        <v>1.129084163658832</v>
+        <v>1.14258349607943</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.968493312435703</v>
+        <v>7.719477896422085</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09420848291103144</v>
+        <v>0.09421325333790363</v>
       </c>
       <c r="C34">
-        <v>2558.458649849897</v>
+        <v>2523.316437058497</v>
       </c>
       <c r="D34">
-        <v>3555.89722516312</v>
+        <v>3555.546842850259</v>
       </c>
       <c r="E34">
-        <v>-832.2444725406001</v>
+        <v>-797.4526420620618</v>
       </c>
       <c r="F34">
-        <v>1113.338575313224</v>
+        <v>1148.130405791762</v>
       </c>
       <c r="G34">
         <v>115.9</v>
@@ -4081,45 +4081,45 @@
         <v>459.8</v>
       </c>
       <c r="M34">
-        <v>59.56361377925747</v>
+        <v>62.34348103449268</v>
       </c>
       <c r="N34">
-        <v>400.2363862207425</v>
+        <v>397.4565189655073</v>
       </c>
       <c r="O34">
-        <v>100.0590965551856</v>
+        <v>99.36412974137683</v>
       </c>
       <c r="P34">
-        <v>300.1772896655569</v>
+        <v>298.0923892241305</v>
       </c>
       <c r="Q34">
-        <v>477.3772896655569</v>
+        <v>475.2923892241305</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1196595336926933</v>
+        <v>0.1205582139371696</v>
       </c>
       <c r="T34">
-        <v>1.14258349607943</v>
+        <v>1.156485793646912</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.719477896422085</v>
+        <v>7.375269913876114</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09421325333790363</v>
+        <v>0.09402602376477584</v>
       </c>
       <c r="C35">
-        <v>2523.316437058497</v>
+        <v>2502.328430027434</v>
       </c>
       <c r="D35">
-        <v>3555.546842850259</v>
+        <v>3569.350666297735</v>
       </c>
       <c r="E35">
-        <v>-797.4526420620618</v>
+        <v>-762.6608115835236</v>
       </c>
       <c r="F35">
-        <v>1148.130405791762</v>
+        <v>1182.9222362703</v>
       </c>
       <c r="G35">
         <v>115.9</v>
@@ -4163,28 +4163,28 @@
         <v>459.8</v>
       </c>
       <c r="M35">
-        <v>62.34348103449268</v>
+        <v>64.23267742947731</v>
       </c>
       <c r="N35">
-        <v>397.4565189655073</v>
+        <v>395.5673225705227</v>
       </c>
       <c r="O35">
-        <v>99.36412974137683</v>
+        <v>98.89183064263068</v>
       </c>
       <c r="P35">
-        <v>298.0923892241305</v>
+        <v>296.675491927892</v>
       </c>
       <c r="Q35">
-        <v>475.2923892241305</v>
+        <v>473.875491927892</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1205582139371696</v>
+        <v>0.121484126916327</v>
       </c>
       <c r="T35">
-        <v>1.156485793646912</v>
+        <v>1.170809372958863</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.375269913876114</v>
+        <v>7.158350210526818</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09402602376477584</v>
+        <v>0.09383879419164803</v>
       </c>
       <c r="C36">
-        <v>2502.328430027434</v>
+        <v>2481.448022864983</v>
       </c>
       <c r="D36">
-        <v>3569.350666297735</v>
+        <v>3583.262089613821</v>
       </c>
       <c r="E36">
-        <v>-762.6608115835236</v>
+        <v>-727.8689811049853</v>
       </c>
       <c r="F36">
-        <v>1182.9222362703</v>
+        <v>1217.714066748839</v>
       </c>
       <c r="G36">
         <v>115.9</v>
@@ -4245,28 +4245,28 @@
         <v>459.8</v>
       </c>
       <c r="M36">
-        <v>64.23267742947731</v>
+        <v>66.12187382446194</v>
       </c>
       <c r="N36">
-        <v>395.5673225705227</v>
+        <v>393.6781261755381</v>
       </c>
       <c r="O36">
-        <v>98.89183064263068</v>
+        <v>98.41953154388452</v>
       </c>
       <c r="P36">
-        <v>296.675491927892</v>
+        <v>295.2585946316535</v>
       </c>
       <c r="Q36">
-        <v>473.875491927892</v>
+        <v>472.4585946316535</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.121484126916327</v>
+        <v>0.1224385295256124</v>
       </c>
       <c r="T36">
-        <v>1.170809372958863</v>
+        <v>1.185573677788104</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.158350210526818</v>
+        <v>6.953825918797478</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09383879419164803</v>
+        <v>0.09365156461852023</v>
       </c>
       <c r="C37">
-        <v>2481.448022864983</v>
+        <v>2460.676478594261</v>
       </c>
       <c r="D37">
-        <v>3583.262089613821</v>
+        <v>3597.282375821637</v>
       </c>
       <c r="E37">
-        <v>-727.8689811049853</v>
+        <v>-693.0771506264471</v>
       </c>
       <c r="F37">
-        <v>1217.714066748839</v>
+        <v>1252.505897227377</v>
       </c>
       <c r="G37">
         <v>115.9</v>
@@ -4327,28 +4327,28 @@
         <v>459.8</v>
       </c>
       <c r="M37">
-        <v>66.12187382446194</v>
+        <v>68.01107021944657</v>
       </c>
       <c r="N37">
-        <v>393.6781261755381</v>
+        <v>391.7889297805534</v>
       </c>
       <c r="O37">
-        <v>98.41953154388452</v>
+        <v>97.94723244513835</v>
       </c>
       <c r="P37">
-        <v>295.2585946316535</v>
+        <v>293.8416973354151</v>
       </c>
       <c r="Q37">
-        <v>472.4585946316535</v>
+        <v>471.0416973354151</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1224385295256124</v>
+        <v>0.1234227572164379</v>
       </c>
       <c r="T37">
-        <v>1.185573677788104</v>
+        <v>1.20079936714326</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.953825918797478</v>
+        <v>6.76066408771977</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09365156461852023</v>
+        <v>0.09346433504539242</v>
       </c>
       <c r="C38">
-        <v>2460.676478594261</v>
+        <v>2440.015080083437</v>
       </c>
       <c r="D38">
-        <v>3597.282375821637</v>
+        <v>3611.412807789352</v>
       </c>
       <c r="E38">
-        <v>-693.0771506264473</v>
+        <v>-658.285320147909</v>
       </c>
       <c r="F38">
-        <v>1252.505897227377</v>
+        <v>1287.297727705915</v>
       </c>
       <c r="G38">
         <v>115.9</v>
@@ -4409,28 +4409,28 @@
         <v>459.8</v>
       </c>
       <c r="M38">
-        <v>68.01107021944655</v>
+        <v>69.90026661443117</v>
       </c>
       <c r="N38">
-        <v>391.7889297805535</v>
+        <v>389.8997333855688</v>
       </c>
       <c r="O38">
-        <v>97.94723244513837</v>
+        <v>97.47493334639221</v>
       </c>
       <c r="P38">
-        <v>293.8416973354151</v>
+        <v>292.4248000391766</v>
       </c>
       <c r="Q38">
-        <v>471.0416973354151</v>
+        <v>469.6248000391766</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1234227572164379</v>
+        <v>0.1244382302307816</v>
       </c>
       <c r="T38">
-        <v>1.20079936714326</v>
+        <v>1.216508411716039</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.760664087719773</v>
+        <v>6.57794343670032</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09346433504539242</v>
+        <v>0.09327710547226463</v>
       </c>
       <c r="C39">
-        <v>2440.015080083437</v>
+        <v>2419.465130437032</v>
       </c>
       <c r="D39">
-        <v>3611.412807789352</v>
+        <v>3625.654688621485</v>
       </c>
       <c r="E39">
-        <v>-658.285320147909</v>
+        <v>-623.4934896693708</v>
       </c>
       <c r="F39">
-        <v>1287.297727705915</v>
+        <v>1322.089558184453</v>
       </c>
       <c r="G39">
         <v>115.9</v>
@@ -4491,28 +4491,28 @@
         <v>459.8</v>
       </c>
       <c r="M39">
-        <v>69.90026661443117</v>
+        <v>71.78946300941581</v>
       </c>
       <c r="N39">
-        <v>389.8997333855688</v>
+        <v>388.0105369905842</v>
       </c>
       <c r="O39">
-        <v>97.47493334639221</v>
+        <v>97.00263424764606</v>
       </c>
       <c r="P39">
-        <v>292.4248000391766</v>
+        <v>291.0079027429382</v>
       </c>
       <c r="Q39">
-        <v>469.6248000391766</v>
+        <v>468.2079027429382</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1244382302307816</v>
+        <v>0.1254864604391365</v>
       </c>
       <c r="T39">
-        <v>1.216508411716039</v>
+        <v>1.232724199662134</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.57794343670032</v>
+        <v>6.404839662050311</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09327710547226463</v>
+        <v>0.09308987589913682</v>
       </c>
       <c r="C40">
-        <v>2419.465130437032</v>
+        <v>2399.027953396521</v>
       </c>
       <c r="D40">
-        <v>3625.654688621485</v>
+        <v>3640.009342059513</v>
       </c>
       <c r="E40">
-        <v>-623.4934896693708</v>
+        <v>-588.7016591908325</v>
       </c>
       <c r="F40">
-        <v>1322.089558184453</v>
+        <v>1356.881388662991</v>
       </c>
       <c r="G40">
         <v>115.9</v>
@@ -4573,28 +4573,28 @@
         <v>459.8</v>
       </c>
       <c r="M40">
-        <v>71.78946300941581</v>
+        <v>73.67865940440043</v>
       </c>
       <c r="N40">
-        <v>388.0105369905842</v>
+        <v>386.1213405955996</v>
       </c>
       <c r="O40">
-        <v>97.00263424764606</v>
+        <v>96.53033514889989</v>
       </c>
       <c r="P40">
-        <v>291.0079027429382</v>
+        <v>289.5910054466997</v>
       </c>
       <c r="Q40">
-        <v>468.2079027429382</v>
+        <v>466.7910054466997</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1254864604391365</v>
+        <v>0.126569058851044</v>
       </c>
       <c r="T40">
-        <v>1.232724199662134</v>
+        <v>1.24947165278679</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.404839662050311</v>
+        <v>6.24061300404902</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09308987589913682</v>
+        <v>0.09320264632600903</v>
       </c>
       <c r="C41">
-        <v>2399.027953396521</v>
+        <v>2355.576576687172</v>
       </c>
       <c r="D41">
-        <v>3640.009342059513</v>
+        <v>3631.349795828702</v>
       </c>
       <c r="E41">
-        <v>-588.7016591908325</v>
+        <v>-553.9098287122943</v>
       </c>
       <c r="F41">
-        <v>1356.881388662991</v>
+        <v>1391.67321914153</v>
       </c>
       <c r="G41">
         <v>115.9</v>
@@ -4655,45 +4655,45 @@
         <v>459.8</v>
       </c>
       <c r="M41">
-        <v>73.67865940440043</v>
+        <v>76.9595290185266</v>
       </c>
       <c r="N41">
-        <v>386.1213405955996</v>
+        <v>382.8404709814734</v>
       </c>
       <c r="O41">
-        <v>96.53033514889989</v>
+        <v>95.71011774536835</v>
       </c>
       <c r="P41">
-        <v>289.5910054466997</v>
+        <v>287.1303532361051</v>
       </c>
       <c r="Q41">
-        <v>466.7910054466997</v>
+        <v>464.3303532361051</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.126569058851044</v>
+        <v>0.1276877438766817</v>
       </c>
       <c r="T41">
-        <v>1.24947165278679</v>
+        <v>1.266777354348933</v>
       </c>
       <c r="U41">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>6.24061300404902</v>
+        <v>5.974568787827581</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09320264632600903</v>
+        <v>0.09302291675288123</v>
       </c>
       <c r="C42">
-        <v>2355.576576687172</v>
+        <v>2334.60559831943</v>
       </c>
       <c r="D42">
-        <v>3631.349795828702</v>
+        <v>3645.170647939497</v>
       </c>
       <c r="E42">
-        <v>-553.9098287122943</v>
+        <v>-519.117998233756</v>
       </c>
       <c r="F42">
-        <v>1391.67321914153</v>
+        <v>1426.465049620068</v>
       </c>
       <c r="G42">
         <v>115.9</v>
@@ -4737,28 +4737,28 @@
         <v>459.8</v>
       </c>
       <c r="M42">
-        <v>76.9595290185266</v>
+        <v>78.88351724398976</v>
       </c>
       <c r="N42">
-        <v>382.8404709814734</v>
+        <v>380.9164827560103</v>
       </c>
       <c r="O42">
-        <v>95.71011774536835</v>
+        <v>95.22912068900257</v>
       </c>
       <c r="P42">
-        <v>287.1303532361051</v>
+        <v>285.6873620670077</v>
       </c>
       <c r="Q42">
-        <v>464.3303532361051</v>
+        <v>462.8873620670077</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1276877438766817</v>
+        <v>0.1288443504286123</v>
       </c>
       <c r="T42">
-        <v>1.266777354348933</v>
+        <v>1.284669689862336</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.974568787827581</v>
+        <v>5.828847597880568</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09302291675288123</v>
+        <v>0.0928431871797534</v>
       </c>
       <c r="C43">
-        <v>2334.60559831943</v>
+        <v>2313.740225715204</v>
       </c>
       <c r="D43">
-        <v>3645.170647939497</v>
+        <v>3659.097105813811</v>
       </c>
       <c r="E43">
-        <v>-519.117998233756</v>
+        <v>-484.3261677552177</v>
       </c>
       <c r="F43">
-        <v>1426.465049620068</v>
+        <v>1461.256880098606</v>
       </c>
       <c r="G43">
         <v>115.9</v>
@@ -4819,28 +4819,28 @@
         <v>459.8</v>
       </c>
       <c r="M43">
-        <v>78.88351724398976</v>
+        <v>80.80750546945292</v>
       </c>
       <c r="N43">
-        <v>380.9164827560103</v>
+        <v>378.9924945305471</v>
       </c>
       <c r="O43">
-        <v>95.22912068900257</v>
+        <v>94.74812363263678</v>
       </c>
       <c r="P43">
-        <v>285.6873620670077</v>
+        <v>284.2443708979104</v>
       </c>
       <c r="Q43">
-        <v>462.8873620670077</v>
+        <v>461.4443708979103</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1288443504286123</v>
+        <v>0.1300408399650921</v>
       </c>
       <c r="T43">
-        <v>1.284669689862336</v>
+        <v>1.303179002462408</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.828847597880568</v>
+        <v>5.690065512216744</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0928431871797534</v>
+        <v>0.09266345760662562</v>
       </c>
       <c r="C44">
-        <v>2313.740225715205</v>
+        <v>2292.981673924324</v>
       </c>
       <c r="D44">
-        <v>3659.097105813811</v>
+        <v>3673.130384501469</v>
       </c>
       <c r="E44">
-        <v>-484.326167755218</v>
+        <v>-449.5343372766797</v>
       </c>
       <c r="F44">
-        <v>1461.256880098606</v>
+        <v>1496.048710577144</v>
       </c>
       <c r="G44">
         <v>115.9</v>
@@ -4901,28 +4901,28 @@
         <v>459.8</v>
       </c>
       <c r="M44">
-        <v>80.80750546945291</v>
+        <v>82.73149369491608</v>
       </c>
       <c r="N44">
-        <v>378.9924945305471</v>
+        <v>377.0685063050839</v>
       </c>
       <c r="O44">
-        <v>94.74812363263678</v>
+        <v>94.26712657627098</v>
       </c>
       <c r="P44">
-        <v>284.2443708979104</v>
+        <v>282.8013797288129</v>
       </c>
       <c r="Q44">
-        <v>461.4443708979103</v>
+        <v>460.0013797288129</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1300408399650921</v>
+        <v>0.1312793115905712</v>
       </c>
       <c r="T44">
-        <v>1.303179002462408</v>
+        <v>1.322337764627395</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.690065512216745</v>
+        <v>5.557738407281471</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09266345760662562</v>
+        <v>0.09248372803349782</v>
       </c>
       <c r="C45">
-        <v>2292.981673924324</v>
+        <v>2272.331176708106</v>
       </c>
       <c r="D45">
-        <v>3673.130384501469</v>
+        <v>3687.271717763789</v>
       </c>
       <c r="E45">
-        <v>-449.5343372766797</v>
+        <v>-414.7425067981412</v>
       </c>
       <c r="F45">
-        <v>1496.048710577144</v>
+        <v>1530.840541055683</v>
       </c>
       <c r="G45">
         <v>115.9</v>
@@ -4983,28 +4983,28 @@
         <v>459.8</v>
       </c>
       <c r="M45">
-        <v>82.73149369491608</v>
+        <v>84.65548192037926</v>
       </c>
       <c r="N45">
-        <v>377.0685063050839</v>
+        <v>375.1445180796208</v>
       </c>
       <c r="O45">
-        <v>94.26712657627098</v>
+        <v>93.78612951990519</v>
       </c>
       <c r="P45">
-        <v>282.8013797288129</v>
+        <v>281.3583885597155</v>
       </c>
       <c r="Q45">
-        <v>460.0013797288129</v>
+        <v>458.5583885597155</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1312793115905712</v>
+        <v>0.1325620143455318</v>
       </c>
       <c r="T45">
-        <v>1.322337764627395</v>
+        <v>1.342180768298275</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.557738407281471</v>
+        <v>5.431426170752347</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09248372803349782</v>
+        <v>0.09230399846037002</v>
       </c>
       <c r="C46">
-        <v>2272.331176708106</v>
+        <v>2251.789986900921</v>
       </c>
       <c r="D46">
-        <v>3687.271717763789</v>
+        <v>3701.522358435142</v>
       </c>
       <c r="E46">
-        <v>-414.7425067981412</v>
+        <v>-379.950676319603</v>
       </c>
       <c r="F46">
-        <v>1530.840541055683</v>
+        <v>1565.632371534221</v>
       </c>
       <c r="G46">
         <v>115.9</v>
@@ -5065,28 +5065,28 @@
         <v>459.8</v>
       </c>
       <c r="M46">
-        <v>84.65548192037926</v>
+        <v>86.57947014584242</v>
       </c>
       <c r="N46">
-        <v>375.1445180796208</v>
+        <v>373.2205298541576</v>
       </c>
       <c r="O46">
-        <v>93.78612951990519</v>
+        <v>93.30513246353939</v>
       </c>
       <c r="P46">
-        <v>281.3583885597155</v>
+        <v>279.9153973906182</v>
       </c>
       <c r="Q46">
-        <v>458.5583885597155</v>
+        <v>457.1153973906182</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1325620143455318</v>
+        <v>0.1338913608370364</v>
       </c>
       <c r="T46">
-        <v>1.342180768298275</v>
+        <v>1.362745335739004</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.431426170752347</v>
+        <v>5.310727811402295</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09230399846037002</v>
+        <v>0.09212426888724222</v>
       </c>
       <c r="C47">
-        <v>2251.789986900921</v>
+        <v>2231.359376780202</v>
       </c>
       <c r="D47">
-        <v>3701.522358435142</v>
+        <v>3715.883578792961</v>
       </c>
       <c r="E47">
-        <v>-379.950676319603</v>
+        <v>-345.1588458410647</v>
       </c>
       <c r="F47">
-        <v>1565.632371534221</v>
+        <v>1600.424202012759</v>
       </c>
       <c r="G47">
         <v>115.9</v>
@@ -5147,28 +5147,28 @@
         <v>459.8</v>
       </c>
       <c r="M47">
-        <v>86.57947014584242</v>
+        <v>88.50345837130558</v>
       </c>
       <c r="N47">
-        <v>373.2205298541576</v>
+        <v>371.2965416286944</v>
       </c>
       <c r="O47">
-        <v>93.30513246353939</v>
+        <v>92.8241354071736</v>
       </c>
       <c r="P47">
-        <v>279.9153973906182</v>
+        <v>278.4724062215208</v>
       </c>
       <c r="Q47">
-        <v>457.1153973906182</v>
+        <v>455.6724062215208</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1338913608370364</v>
+        <v>0.1352699423837819</v>
       </c>
       <c r="T47">
-        <v>1.362745335739004</v>
+        <v>1.384071553825686</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.310727811402295</v>
+        <v>5.195277206806592</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09212426888724222</v>
+        <v>0.09194453931411439</v>
       </c>
       <c r="C48">
-        <v>2231.359376780202</v>
+        <v>2211.04063844509</v>
       </c>
       <c r="D48">
-        <v>3715.883578792961</v>
+        <v>3730.356670936388</v>
       </c>
       <c r="E48">
-        <v>-345.1588458410647</v>
+        <v>-310.3670153625264</v>
       </c>
       <c r="F48">
-        <v>1600.424202012759</v>
+        <v>1635.216032491297</v>
       </c>
       <c r="G48">
         <v>115.9</v>
@@ -5229,28 +5229,28 @@
         <v>459.8</v>
       </c>
       <c r="M48">
-        <v>88.50345837130558</v>
+        <v>90.42744659676876</v>
       </c>
       <c r="N48">
-        <v>371.2965416286944</v>
+        <v>369.3725534032312</v>
       </c>
       <c r="O48">
-        <v>92.8241354071736</v>
+        <v>92.34313835080781</v>
       </c>
       <c r="P48">
-        <v>278.4724062215208</v>
+        <v>277.0294150524234</v>
       </c>
       <c r="Q48">
-        <v>455.6724062215208</v>
+        <v>454.2294150524234</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1352699423837819</v>
+        <v>0.1367005458756875</v>
       </c>
       <c r="T48">
-        <v>1.384071553825686</v>
+        <v>1.406202534859036</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.195277206806592</v>
+        <v>5.084739393895813</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09194453931411439</v>
+        <v>0.09176480974098661</v>
       </c>
       <c r="C49">
-        <v>2211.04063844509</v>
+        <v>2190.835084203956</v>
       </c>
       <c r="D49">
-        <v>3730.356670936388</v>
+        <v>3744.942947173792</v>
       </c>
       <c r="E49">
-        <v>-310.3670153625264</v>
+        <v>-275.5751848839882</v>
       </c>
       <c r="F49">
-        <v>1635.216032491297</v>
+        <v>1670.007862969836</v>
       </c>
       <c r="G49">
         <v>115.9</v>
@@ -5311,28 +5311,28 @@
         <v>459.8</v>
       </c>
       <c r="M49">
-        <v>90.42744659676876</v>
+        <v>92.35143482223192</v>
       </c>
       <c r="N49">
-        <v>369.3725534032312</v>
+        <v>367.4485651777681</v>
       </c>
       <c r="O49">
-        <v>92.34313835080781</v>
+        <v>91.86214129444203</v>
       </c>
       <c r="P49">
-        <v>277.0294150524234</v>
+        <v>275.5864238833261</v>
       </c>
       <c r="Q49">
-        <v>454.2294150524234</v>
+        <v>452.7864238833261</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1367005458756875</v>
+        <v>0.1381861725788204</v>
       </c>
       <c r="T49">
-        <v>1.406202534859036</v>
+        <v>1.429184707470591</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.084739393895813</v>
+        <v>4.978807323189651</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09176480974098659</v>
+        <v>0.09158508016785878</v>
       </c>
       <c r="C50">
-        <v>2190.835084203959</v>
+        <v>2170.744046971077</v>
       </c>
       <c r="D50">
-        <v>3744.942947173794</v>
+        <v>3759.643740419451</v>
       </c>
       <c r="E50">
-        <v>-275.5751848839884</v>
+        <v>-240.7833544054502</v>
       </c>
       <c r="F50">
-        <v>1670.007862969836</v>
+        <v>1704.799693448374</v>
       </c>
       <c r="G50">
         <v>115.9</v>
@@ -5393,28 +5393,28 @@
         <v>459.8</v>
       </c>
       <c r="M50">
-        <v>92.35143482223191</v>
+        <v>94.27542304769507</v>
       </c>
       <c r="N50">
-        <v>367.4485651777681</v>
+        <v>365.5245769523049</v>
       </c>
       <c r="O50">
-        <v>91.86214129444203</v>
+        <v>91.38114423807623</v>
       </c>
       <c r="P50">
-        <v>275.5864238833261</v>
+        <v>274.1434327142287</v>
       </c>
       <c r="Q50">
-        <v>452.7864238833261</v>
+        <v>451.3434327142287</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1381861725788204</v>
+        <v>0.1397300591526643</v>
       </c>
       <c r="T50">
-        <v>1.429184707470591</v>
+        <v>1.453068141753188</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.978807323189651</v>
+        <v>4.877199010471495</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09158508016785878</v>
+        <v>0.09140535059473098</v>
       </c>
       <c r="C51">
-        <v>2170.744046971077</v>
+        <v>2150.768880672647</v>
       </c>
       <c r="D51">
-        <v>3759.643740419451</v>
+        <v>3774.460404599559</v>
       </c>
       <c r="E51">
-        <v>-240.7833544054502</v>
+        <v>-205.9915239269119</v>
       </c>
       <c r="F51">
-        <v>1704.799693448374</v>
+        <v>1739.591523926912</v>
       </c>
       <c r="G51">
         <v>115.9</v>
@@ -5475,28 +5475,28 @@
         <v>459.8</v>
       </c>
       <c r="M51">
-        <v>94.27542304769507</v>
+        <v>96.19941127315823</v>
       </c>
       <c r="N51">
-        <v>365.5245769523049</v>
+        <v>363.6005887268418</v>
       </c>
       <c r="O51">
-        <v>91.38114423807623</v>
+        <v>90.90014718171045</v>
       </c>
       <c r="P51">
-        <v>274.1434327142287</v>
+        <v>272.7004415451314</v>
       </c>
       <c r="Q51">
-        <v>451.3434327142287</v>
+        <v>449.9004415451313</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1397300591526643</v>
+        <v>0.141335701189462</v>
       </c>
       <c r="T51">
-        <v>1.453068141753188</v>
+        <v>1.477906913407089</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.877199010471495</v>
+        <v>4.779655030262066</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09140535059473098</v>
+        <v>0.0912256210216032</v>
       </c>
       <c r="C52">
-        <v>2150.768880672647</v>
+        <v>2130.910960662472</v>
       </c>
       <c r="D52">
-        <v>3774.460404599559</v>
+        <v>3789.394315067922</v>
       </c>
       <c r="E52">
-        <v>-205.9915239269119</v>
+        <v>-171.1996934483736</v>
       </c>
       <c r="F52">
-        <v>1739.591523926912</v>
+        <v>1774.38335440545</v>
       </c>
       <c r="G52">
         <v>115.9</v>
@@ -5557,28 +5557,28 @@
         <v>459.8</v>
       </c>
       <c r="M52">
-        <v>96.19941127315823</v>
+        <v>98.12339949862141</v>
       </c>
       <c r="N52">
-        <v>363.6005887268418</v>
+        <v>361.6766005013786</v>
       </c>
       <c r="O52">
-        <v>90.90014718171045</v>
+        <v>90.41915012534466</v>
       </c>
       <c r="P52">
-        <v>272.7004415451314</v>
+        <v>271.2574503760339</v>
       </c>
       <c r="Q52">
-        <v>449.9004415451313</v>
+        <v>448.4574503760339</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.141335701189462</v>
+        <v>0.1430068796359249</v>
       </c>
       <c r="T52">
-        <v>1.477906913407089</v>
+        <v>1.503759512475435</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.779655030262066</v>
+        <v>4.685936304178496</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0912256210216032</v>
+        <v>0.0910458914484754</v>
       </c>
       <c r="C53">
-        <v>2130.910960662472</v>
+        <v>2111.171684147548</v>
       </c>
       <c r="D53">
-        <v>3789.394315067922</v>
+        <v>3804.446869031537</v>
       </c>
       <c r="E53">
-        <v>-171.1996934483736</v>
+        <v>-136.4078629698354</v>
       </c>
       <c r="F53">
-        <v>1774.38335440545</v>
+        <v>1809.175184883989</v>
       </c>
       <c r="G53">
         <v>115.9</v>
@@ -5639,28 +5639,28 @@
         <v>459.8</v>
       </c>
       <c r="M53">
-        <v>98.12339949862141</v>
+        <v>100.0473877240846</v>
       </c>
       <c r="N53">
-        <v>361.6766005013786</v>
+        <v>359.7526122759155</v>
       </c>
       <c r="O53">
-        <v>90.41915012534466</v>
+        <v>89.93815306897886</v>
       </c>
       <c r="P53">
-        <v>271.2574503760339</v>
+        <v>269.8144592069366</v>
       </c>
       <c r="Q53">
-        <v>448.4574503760339</v>
+        <v>447.0144592069366</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1430068796359249</v>
+        <v>0.1447476905176571</v>
       </c>
       <c r="T53">
-        <v>1.503759512475435</v>
+        <v>1.530689303171628</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.685936304178496</v>
+        <v>4.595822144482755</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0910458914484754</v>
+        <v>0.09086616187534757</v>
       </c>
       <c r="C54">
-        <v>2111.171684147548</v>
+        <v>2091.552470623829</v>
       </c>
       <c r="D54">
-        <v>3804.446869031537</v>
+        <v>3819.619485986356</v>
       </c>
       <c r="E54">
-        <v>-136.4078629698354</v>
+        <v>-101.6160324912971</v>
       </c>
       <c r="F54">
-        <v>1809.175184883989</v>
+        <v>1843.967015362527</v>
       </c>
       <c r="G54">
         <v>115.9</v>
@@ -5721,28 +5721,28 @@
         <v>459.8</v>
       </c>
       <c r="M54">
-        <v>100.0473877240846</v>
+        <v>101.9713759495477</v>
       </c>
       <c r="N54">
-        <v>359.7526122759155</v>
+        <v>357.8286240504523</v>
       </c>
       <c r="O54">
-        <v>89.93815306897886</v>
+        <v>89.45715601261307</v>
       </c>
       <c r="P54">
-        <v>269.8144592069366</v>
+        <v>268.3714680378392</v>
       </c>
       <c r="Q54">
-        <v>447.0144592069366</v>
+        <v>445.5714680378392</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1447476905176571</v>
+        <v>0.1465625784581863</v>
       </c>
       <c r="T54">
-        <v>1.530689303171628</v>
+        <v>1.558765042408085</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.595822144482755</v>
+        <v>4.509108519115156</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09086616187534757</v>
+        <v>0.09169893230221977</v>
       </c>
       <c r="C55">
-        <v>2091.552470623829</v>
+        <v>1987.459111977056</v>
       </c>
       <c r="D55">
-        <v>3819.619485986356</v>
+        <v>3750.317957818121</v>
       </c>
       <c r="E55">
-        <v>-101.6160324912971</v>
+        <v>-66.82420201275886</v>
       </c>
       <c r="F55">
-        <v>1843.967015362527</v>
+        <v>1878.758845841065</v>
       </c>
       <c r="G55">
         <v>115.9</v>
@@ -5803,45 +5803,45 @@
         <v>459.8</v>
       </c>
       <c r="M55">
-        <v>101.9713759495477</v>
+        <v>108.5922612896136</v>
       </c>
       <c r="N55">
-        <v>357.8286240504523</v>
+        <v>351.2077387103864</v>
       </c>
       <c r="O55">
-        <v>89.45715601261307</v>
+        <v>87.80193467759661</v>
       </c>
       <c r="P55">
-        <v>268.3714680378392</v>
+        <v>263.4058040327898</v>
       </c>
       <c r="Q55">
-        <v>445.5714680378392</v>
+        <v>440.6058040327898</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1465625784581863</v>
+        <v>0.148456374570043</v>
       </c>
       <c r="T55">
-        <v>1.558765042408085</v>
+        <v>1.58806146595917</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.509108519115156</v>
+        <v>4.234187542827954</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09169893230221977</v>
+        <v>0.09153795272909199</v>
       </c>
       <c r="C56">
-        <v>1987.459111977056</v>
+        <v>1965.866923107291</v>
       </c>
       <c r="D56">
-        <v>3750.317957818121</v>
+        <v>3763.517599426894</v>
       </c>
       <c r="E56">
-        <v>-66.82420201275886</v>
+        <v>-32.0323715342206</v>
       </c>
       <c r="F56">
-        <v>1878.758845841065</v>
+        <v>1913.550676319603</v>
       </c>
       <c r="G56">
         <v>115.9</v>
@@ -5885,28 +5885,28 @@
         <v>459.8</v>
       </c>
       <c r="M56">
-        <v>108.5922612896136</v>
+        <v>110.6032290912731</v>
       </c>
       <c r="N56">
-        <v>351.2077387103864</v>
+        <v>349.1967709087269</v>
       </c>
       <c r="O56">
-        <v>87.80193467759661</v>
+        <v>87.29919272718173</v>
       </c>
       <c r="P56">
-        <v>263.4058040327898</v>
+        <v>261.8975781815452</v>
       </c>
       <c r="Q56">
-        <v>440.6058040327898</v>
+        <v>439.0975781815452</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.148456374570043</v>
+        <v>0.1504343393979822</v>
       </c>
       <c r="T56">
-        <v>1.58806146595917</v>
+        <v>1.618659952779193</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.234187542827954</v>
+        <v>4.157202314776537</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09153795272909199</v>
+        <v>0.09137697315596417</v>
       </c>
       <c r="C57">
-        <v>1965.866923107291</v>
+        <v>1944.367977492816</v>
       </c>
       <c r="D57">
-        <v>3763.517599426894</v>
+        <v>3776.810484290958</v>
       </c>
       <c r="E57">
-        <v>-32.0323715342206</v>
+        <v>2.759458944317657</v>
       </c>
       <c r="F57">
-        <v>1913.550676319603</v>
+        <v>1948.342506798142</v>
       </c>
       <c r="G57">
         <v>115.9</v>
@@ -5967,28 +5967,28 @@
         <v>459.8</v>
       </c>
       <c r="M57">
-        <v>110.6032290912731</v>
+        <v>112.6141968929326</v>
       </c>
       <c r="N57">
-        <v>349.1967709087269</v>
+        <v>347.1858031070674</v>
       </c>
       <c r="O57">
-        <v>87.29919272718173</v>
+        <v>86.79645077676685</v>
       </c>
       <c r="P57">
-        <v>261.8975781815452</v>
+        <v>260.3893523303005</v>
       </c>
       <c r="Q57">
-        <v>439.0975781815452</v>
+        <v>437.5893523303005</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1504343393979822</v>
+        <v>0.1525022117181004</v>
       </c>
       <c r="T57">
-        <v>1.618659952779193</v>
+        <v>1.650649279909216</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.157202314776537</v>
+        <v>4.082966559155526</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09137697315596417</v>
+        <v>0.09121599358283639</v>
       </c>
       <c r="C58">
-        <v>1944.367977492816</v>
+        <v>1922.963266651697</v>
       </c>
       <c r="D58">
-        <v>3776.810484290958</v>
+        <v>3790.197603928377</v>
       </c>
       <c r="E58">
-        <v>2.759458944317657</v>
+        <v>37.55128942285592</v>
       </c>
       <c r="F58">
-        <v>1948.342506798142</v>
+        <v>1983.13433727668</v>
       </c>
       <c r="G58">
         <v>115.9</v>
@@ -6049,28 +6049,28 @@
         <v>459.8</v>
       </c>
       <c r="M58">
-        <v>112.6141968929326</v>
+        <v>114.6251646945921</v>
       </c>
       <c r="N58">
-        <v>347.1858031070674</v>
+        <v>345.1748353054079</v>
       </c>
       <c r="O58">
-        <v>86.79645077676685</v>
+        <v>86.29370882635197</v>
       </c>
       <c r="P58">
-        <v>260.3893523303005</v>
+        <v>258.8811264790559</v>
       </c>
       <c r="Q58">
-        <v>437.5893523303005</v>
+        <v>436.0811264790559</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1525022117181004</v>
+        <v>0.1546662641461311</v>
       </c>
       <c r="T58">
-        <v>1.650649279909216</v>
+        <v>1.684126482719706</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.082966559155526</v>
+        <v>4.01133556688964</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09121599358283639</v>
+        <v>0.09257751400970858</v>
       </c>
       <c r="C59">
-        <v>1922.963266651697</v>
+        <v>1777.852801913128</v>
       </c>
       <c r="D59">
-        <v>3790.197603928377</v>
+        <v>3679.878969668346</v>
       </c>
       <c r="E59">
-        <v>37.55128942285592</v>
+        <v>72.34311990139418</v>
       </c>
       <c r="F59">
-        <v>1983.13433727668</v>
+        <v>2017.926167755218</v>
       </c>
       <c r="G59">
         <v>115.9</v>
@@ -6131,45 +6131,45 @@
         <v>459.8</v>
       </c>
       <c r="M59">
-        <v>114.6251646945921</v>
+        <v>123.6988740833949</v>
       </c>
       <c r="N59">
-        <v>345.1748353054079</v>
+        <v>336.1011259166052</v>
       </c>
       <c r="O59">
-        <v>86.29370882635197</v>
+        <v>84.02528147915129</v>
       </c>
       <c r="P59">
-        <v>258.8811264790559</v>
+        <v>252.0758444374539</v>
       </c>
       <c r="Q59">
-        <v>436.0811264790559</v>
+        <v>429.2758444374539</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1546662641461311</v>
+        <v>0.1569333666897823</v>
       </c>
       <c r="T59">
-        <v>1.684126482719706</v>
+        <v>1.719197838044981</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.01133556688964</v>
+        <v>3.717091229868541</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09257751400970857</v>
+        <v>0.09244278443658077</v>
       </c>
       <c r="C60">
-        <v>1777.852801913129</v>
+        <v>1753.690450972192</v>
       </c>
       <c r="D60">
-        <v>3679.878969668347</v>
+        <v>3690.508449205948</v>
       </c>
       <c r="E60">
-        <v>72.34311990139395</v>
+        <v>107.1349503799322</v>
       </c>
       <c r="F60">
-        <v>2017.926167755218</v>
+        <v>2052.717998233756</v>
       </c>
       <c r="G60">
         <v>115.9</v>
@@ -6213,28 +6213,28 @@
         <v>459.8</v>
       </c>
       <c r="M60">
-        <v>123.6988740833949</v>
+        <v>125.8316132917293</v>
       </c>
       <c r="N60">
-        <v>336.1011259166052</v>
+        <v>333.9683867082708</v>
       </c>
       <c r="O60">
-        <v>84.02528147915129</v>
+        <v>83.49209667706769</v>
       </c>
       <c r="P60">
-        <v>252.0758444374539</v>
+        <v>250.4762900312031</v>
       </c>
       <c r="Q60">
-        <v>429.2758444374539</v>
+        <v>427.6762900312031</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1569333666897823</v>
+        <v>0.1593110596014165</v>
       </c>
       <c r="T60">
-        <v>1.719197838044981</v>
+        <v>1.755979991191001</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.717091229868541</v>
+        <v>3.654089683599583</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09244278443658077</v>
+        <v>0.09230805486345296</v>
       </c>
       <c r="C61">
-        <v>1753.690450972192</v>
+        <v>1729.589685287611</v>
       </c>
       <c r="D61">
-        <v>3690.508449205948</v>
+        <v>3701.199513999905</v>
       </c>
       <c r="E61">
-        <v>107.1349503799322</v>
+        <v>141.9267808584702</v>
       </c>
       <c r="F61">
-        <v>2052.717998233756</v>
+        <v>2087.509828712294</v>
       </c>
       <c r="G61">
         <v>115.9</v>
@@ -6295,28 +6295,28 @@
         <v>459.8</v>
       </c>
       <c r="M61">
-        <v>125.8316132917293</v>
+        <v>127.9643525000636</v>
       </c>
       <c r="N61">
-        <v>333.9683867082708</v>
+        <v>331.8356474999364</v>
       </c>
       <c r="O61">
-        <v>83.49209667706769</v>
+        <v>82.9589118749841</v>
       </c>
       <c r="P61">
-        <v>250.4762900312031</v>
+        <v>248.8767356249523</v>
       </c>
       <c r="Q61">
-        <v>427.6762900312031</v>
+        <v>426.0767356249523</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1593110596014165</v>
+        <v>0.1618076371586324</v>
       </c>
       <c r="T61">
-        <v>1.755979991191001</v>
+        <v>1.794601251994322</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.654089683599583</v>
+        <v>3.593188188872924</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09230805486345296</v>
+        <v>0.09217332529032515</v>
       </c>
       <c r="C62">
-        <v>1729.589685287611</v>
+        <v>1705.551041634907</v>
       </c>
       <c r="D62">
-        <v>3701.199513999905</v>
+        <v>3711.95270082574</v>
       </c>
       <c r="E62">
-        <v>141.9267808584702</v>
+        <v>176.7186113370087</v>
       </c>
       <c r="F62">
-        <v>2087.509828712294</v>
+        <v>2122.301659190833</v>
       </c>
       <c r="G62">
         <v>115.9</v>
@@ -6377,28 +6377,28 @@
         <v>459.8</v>
       </c>
       <c r="M62">
-        <v>127.9643525000636</v>
+        <v>130.097091708398</v>
       </c>
       <c r="N62">
-        <v>331.8356474999364</v>
+        <v>329.7029082916019</v>
       </c>
       <c r="O62">
-        <v>82.9589118749841</v>
+        <v>82.42572707290049</v>
       </c>
       <c r="P62">
-        <v>248.8767356249523</v>
+        <v>247.2771812187015</v>
       </c>
       <c r="Q62">
-        <v>426.0767356249523</v>
+        <v>424.4771812187014</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1618076371586324</v>
+        <v>0.1644322443341671</v>
       </c>
       <c r="T62">
-        <v>1.794601251994322</v>
+        <v>1.835203090274737</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.593188188872924</v>
+        <v>3.53428346446517</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09217332529032515</v>
+        <v>0.09334059571719737</v>
       </c>
       <c r="C63">
-        <v>1705.551041634907</v>
+        <v>1579.619153943014</v>
       </c>
       <c r="D63">
-        <v>3711.95270082574</v>
+        <v>3620.812643612385</v>
       </c>
       <c r="E63">
-        <v>176.7186113370087</v>
+        <v>211.5104418155468</v>
       </c>
       <c r="F63">
-        <v>2122.301659190833</v>
+        <v>2157.093489669371</v>
       </c>
       <c r="G63">
         <v>115.9</v>
@@ -6459,45 +6459,45 @@
         <v>459.8</v>
       </c>
       <c r="M63">
-        <v>130.097091708398</v>
+        <v>138.2696926878067</v>
       </c>
       <c r="N63">
-        <v>329.7029082916019</v>
+        <v>321.5303073121934</v>
       </c>
       <c r="O63">
-        <v>82.42572707290049</v>
+        <v>80.38257682804834</v>
       </c>
       <c r="P63">
-        <v>247.2771812187015</v>
+        <v>241.147730484145</v>
       </c>
       <c r="Q63">
-        <v>424.4771812187014</v>
+        <v>418.347730484145</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1644322443341671</v>
+        <v>0.1671949887294668</v>
       </c>
       <c r="T63">
-        <v>1.835203090274737</v>
+        <v>1.877941867412015</v>
       </c>
       <c r="U63">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.53428346446517</v>
+        <v>3.325385274690406</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09334059571719737</v>
+        <v>0.09322686614406957</v>
       </c>
       <c r="C64">
-        <v>1579.619153943014</v>
+        <v>1553.510028222638</v>
       </c>
       <c r="D64">
-        <v>3620.812643612385</v>
+        <v>3629.495348370547</v>
       </c>
       <c r="E64">
-        <v>211.5104418155468</v>
+        <v>246.3022722940852</v>
       </c>
       <c r="F64">
-        <v>2157.093489669371</v>
+        <v>2191.885320147909</v>
       </c>
       <c r="G64">
         <v>115.9</v>
@@ -6541,28 +6541,28 @@
         <v>459.8</v>
       </c>
       <c r="M64">
-        <v>138.2696926878067</v>
+        <v>140.499849021481</v>
       </c>
       <c r="N64">
-        <v>321.5303073121934</v>
+        <v>319.300150978519</v>
       </c>
       <c r="O64">
-        <v>80.38257682804834</v>
+        <v>79.82503774462975</v>
       </c>
       <c r="P64">
-        <v>241.147730484145</v>
+        <v>239.4751132338893</v>
       </c>
       <c r="Q64">
-        <v>418.347730484145</v>
+        <v>416.6751132338892</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1671949887294668</v>
+        <v>0.1701070706596475</v>
       </c>
       <c r="T64">
-        <v>1.877941867412015</v>
+        <v>1.922990848718876</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.325385274690406</v>
+        <v>3.272601381441351</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09322686614406957</v>
+        <v>0.09311313657094175</v>
       </c>
       <c r="C65">
-        <v>1553.510028222638</v>
+        <v>1527.442644833347</v>
       </c>
       <c r="D65">
-        <v>3629.495348370547</v>
+        <v>3638.219795459795</v>
       </c>
       <c r="E65">
-        <v>246.3022722940852</v>
+        <v>281.0941027726237</v>
       </c>
       <c r="F65">
-        <v>2191.885320147909</v>
+        <v>2226.677150626448</v>
       </c>
       <c r="G65">
         <v>115.9</v>
@@ -6623,28 +6623,28 @@
         <v>459.8</v>
       </c>
       <c r="M65">
-        <v>140.499849021481</v>
+        <v>142.7300053551553</v>
       </c>
       <c r="N65">
-        <v>319.300150978519</v>
+        <v>317.0699946448447</v>
       </c>
       <c r="O65">
-        <v>79.82503774462975</v>
+        <v>79.26749866121118</v>
       </c>
       <c r="P65">
-        <v>239.4751132338893</v>
+        <v>237.8024959836335</v>
       </c>
       <c r="Q65">
-        <v>416.6751132338892</v>
+        <v>415.0024959836335</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1701070706596475</v>
+        <v>0.1731809349192827</v>
       </c>
       <c r="T65">
-        <v>1.922990848718876</v>
+        <v>1.970542551209452</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.272601381441351</v>
+        <v>3.22146698485633</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09311313657094175</v>
+        <v>0.09299940699781396</v>
       </c>
       <c r="C66">
-        <v>1527.442644833347</v>
+        <v>1501.417305516486</v>
       </c>
       <c r="D66">
-        <v>3638.219795459795</v>
+        <v>3646.986286621471</v>
       </c>
       <c r="E66">
-        <v>281.0941027726237</v>
+        <v>315.8859332511618</v>
       </c>
       <c r="F66">
-        <v>2226.677150626448</v>
+        <v>2261.468981104986</v>
       </c>
       <c r="G66">
         <v>115.9</v>
@@ -6705,28 +6705,28 @@
         <v>459.8</v>
       </c>
       <c r="M66">
-        <v>142.7300053551553</v>
+        <v>144.9601616888296</v>
       </c>
       <c r="N66">
-        <v>317.0699946448447</v>
+        <v>314.8398383111704</v>
       </c>
       <c r="O66">
-        <v>79.26749866121118</v>
+        <v>78.7099595777926</v>
       </c>
       <c r="P66">
-        <v>237.8024959836335</v>
+        <v>236.1298787333778</v>
       </c>
       <c r="Q66">
-        <v>415.0024959836335</v>
+        <v>413.3298787333778</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1731809349192827</v>
+        <v>0.1764304485651828</v>
       </c>
       <c r="T66">
-        <v>1.970542551209452</v>
+        <v>2.020811493842346</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.22146698485633</v>
+        <v>3.171905954320079</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09299940699781396</v>
+        <v>0.09288567742468615</v>
       </c>
       <c r="C67">
-        <v>1501.417305516486</v>
+        <v>1475.434314928674</v>
       </c>
       <c r="D67">
-        <v>3646.986286621471</v>
+        <v>3655.795126512198</v>
       </c>
       <c r="E67">
-        <v>315.8859332511618</v>
+        <v>350.6777637297002</v>
       </c>
       <c r="F67">
-        <v>2261.468981104986</v>
+        <v>2296.260811583524</v>
       </c>
       <c r="G67">
         <v>115.9</v>
@@ -6787,28 +6787,28 @@
         <v>459.8</v>
       </c>
       <c r="M67">
-        <v>144.9601616888296</v>
+        <v>147.1903180225039</v>
       </c>
       <c r="N67">
-        <v>314.8398383111704</v>
+        <v>312.6096819774961</v>
       </c>
       <c r="O67">
-        <v>78.7099595777926</v>
+        <v>78.15242049437403</v>
       </c>
       <c r="P67">
-        <v>236.1298787333778</v>
+        <v>234.4572614831221</v>
       </c>
       <c r="Q67">
-        <v>413.3298787333778</v>
+        <v>411.6572614831221</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1764304485651828</v>
+        <v>0.1798711100726063</v>
       </c>
       <c r="T67">
-        <v>2.020811493842346</v>
+        <v>2.074037433100705</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.171905954320079</v>
+        <v>3.123846773194017</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09288567742468615</v>
+        <v>0.09277194785155835</v>
       </c>
       <c r="C68">
-        <v>1475.434314928674</v>
+        <v>1449.493980677094</v>
       </c>
       <c r="D68">
-        <v>3655.795126512198</v>
+        <v>3664.646622739156</v>
       </c>
       <c r="E68">
-        <v>350.6777637297002</v>
+        <v>385.4695942082383</v>
       </c>
       <c r="F68">
-        <v>2296.260811583524</v>
+        <v>2331.052642062062</v>
       </c>
       <c r="G68">
         <v>115.9</v>
@@ -6869,28 +6869,28 @@
         <v>459.8</v>
       </c>
       <c r="M68">
-        <v>147.1903180225039</v>
+        <v>149.4204743561782</v>
       </c>
       <c r="N68">
-        <v>312.6096819774961</v>
+        <v>310.3795256438218</v>
       </c>
       <c r="O68">
-        <v>78.15242049437403</v>
+        <v>77.59488141095545</v>
       </c>
       <c r="P68">
-        <v>234.4572614831221</v>
+        <v>232.7846442328664</v>
       </c>
       <c r="Q68">
-        <v>411.6572614831221</v>
+        <v>409.9846442328663</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1798711100726063</v>
+        <v>0.1835202965198738</v>
       </c>
       <c r="T68">
-        <v>2.074037433100705</v>
+        <v>2.13048918685957</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.123846773194017</v>
+        <v>3.077222194489629</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09277194785155835</v>
+        <v>0.09265821827843054</v>
       </c>
       <c r="C69">
-        <v>1449.493980677094</v>
+        <v>1423.596613355303</v>
       </c>
       <c r="D69">
-        <v>3664.646622739156</v>
+        <v>3673.541085895904</v>
       </c>
       <c r="E69">
-        <v>385.4695942082383</v>
+        <v>420.2614246867768</v>
       </c>
       <c r="F69">
-        <v>2331.052642062062</v>
+        <v>2365.844472540601</v>
       </c>
       <c r="G69">
         <v>115.9</v>
@@ -6951,28 +6951,28 @@
         <v>459.8</v>
       </c>
       <c r="M69">
-        <v>149.4204743561782</v>
+        <v>151.6506306898525</v>
       </c>
       <c r="N69">
-        <v>310.3795256438218</v>
+        <v>308.1493693101475</v>
       </c>
       <c r="O69">
-        <v>77.59488141095545</v>
+        <v>77.03734232753688</v>
       </c>
       <c r="P69">
-        <v>232.7846442328664</v>
+        <v>231.1120269826106</v>
       </c>
       <c r="Q69">
-        <v>409.9846442328663</v>
+        <v>408.3120269826106</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1835202965198738</v>
+        <v>0.1873975571200955</v>
       </c>
       <c r="T69">
-        <v>2.13048918685957</v>
+        <v>2.190469175228364</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.077222194489629</v>
+        <v>3.031968926923605</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09265821827843054</v>
+        <v>0.09658098870530274</v>
       </c>
       <c r="C70">
-        <v>1423.596613355303</v>
+        <v>1105.028143211858</v>
       </c>
       <c r="D70">
-        <v>3673.541085895904</v>
+        <v>3389.764446230997</v>
       </c>
       <c r="E70">
-        <v>420.2614246867768</v>
+        <v>455.0532551653148</v>
       </c>
       <c r="F70">
-        <v>2365.844472540601</v>
+        <v>2400.636303019139</v>
       </c>
       <c r="G70">
         <v>115.9</v>
@@ -7033,45 +7033,45 @@
         <v>459.8</v>
       </c>
       <c r="M70">
-        <v>151.6506306898525</v>
+        <v>172.6057501870761</v>
       </c>
       <c r="N70">
-        <v>308.1493693101475</v>
+        <v>287.1942498129239</v>
       </c>
       <c r="O70">
-        <v>77.03734232753688</v>
+        <v>71.79856245323097</v>
       </c>
       <c r="P70">
-        <v>231.1120269826106</v>
+        <v>215.3956873596929</v>
       </c>
       <c r="Q70">
-        <v>408.3120269826106</v>
+        <v>392.5956873596929</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1873975571200955</v>
+        <v>0.1915249635654928</v>
       </c>
       <c r="T70">
-        <v>2.190469175228364</v>
+        <v>2.254318840266113</v>
       </c>
       <c r="U70">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.031968926923605</v>
+        <v>2.6638741727993</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09658098870530274</v>
+        <v>0.09652575913217494</v>
       </c>
       <c r="C71">
-        <v>1105.028143211858</v>
+        <v>1073.927045934203</v>
       </c>
       <c r="D71">
-        <v>3389.764446230997</v>
+        <v>3393.45517943188</v>
       </c>
       <c r="E71">
-        <v>455.0532551653148</v>
+        <v>489.8450856438533</v>
       </c>
       <c r="F71">
-        <v>2400.636303019139</v>
+        <v>2435.428133497677</v>
       </c>
       <c r="G71">
         <v>115.9</v>
@@ -7115,28 +7115,28 @@
         <v>459.8</v>
       </c>
       <c r="M71">
-        <v>172.6057501870761</v>
+        <v>175.107282798483</v>
       </c>
       <c r="N71">
-        <v>287.1942498129239</v>
+        <v>284.692717201517</v>
       </c>
       <c r="O71">
-        <v>71.79856245323097</v>
+        <v>71.17317930037925</v>
       </c>
       <c r="P71">
-        <v>215.3956873596929</v>
+        <v>213.5195379011377</v>
       </c>
       <c r="Q71">
-        <v>392.5956873596929</v>
+        <v>390.7195379011378</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1915249635654928</v>
+        <v>0.1959275304405832</v>
       </c>
       <c r="T71">
-        <v>2.254318840266113</v>
+        <v>2.322425149639712</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.6638741727993</v>
+        <v>2.625818827473596</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09652575913217494</v>
+        <v>0.09647052955904714</v>
       </c>
       <c r="C72">
-        <v>1073.927045934203</v>
+        <v>1042.833994264952</v>
       </c>
       <c r="D72">
-        <v>3393.45517943188</v>
+        <v>3397.153958241167</v>
       </c>
       <c r="E72">
-        <v>489.8450856438533</v>
+        <v>524.6369161223913</v>
       </c>
       <c r="F72">
-        <v>2435.428133497677</v>
+        <v>2470.219963976215</v>
       </c>
       <c r="G72">
         <v>115.9</v>
@@ -7197,28 +7197,28 @@
         <v>459.8</v>
       </c>
       <c r="M72">
-        <v>175.107282798483</v>
+        <v>177.6088154098899</v>
       </c>
       <c r="N72">
-        <v>284.692717201517</v>
+        <v>282.1911845901101</v>
       </c>
       <c r="O72">
-        <v>71.17317930037925</v>
+        <v>70.54779614752752</v>
       </c>
       <c r="P72">
-        <v>213.5195379011377</v>
+        <v>211.6433884425826</v>
       </c>
       <c r="Q72">
-        <v>390.7195379011378</v>
+        <v>388.8433884425825</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1959275304405832</v>
+        <v>0.200633722617404</v>
       </c>
       <c r="T72">
-        <v>2.322425149639712</v>
+        <v>2.395228445866662</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.625818827473596</v>
+        <v>2.588835463706362</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09647052955904714</v>
+        <v>0.09641529998591934</v>
       </c>
       <c r="C73">
-        <v>1042.833994264952</v>
+        <v>1011.749014541329</v>
       </c>
       <c r="D73">
-        <v>3397.153958241167</v>
+        <v>3400.860808996082</v>
       </c>
       <c r="E73">
-        <v>524.6369161223909</v>
+        <v>559.4287466009293</v>
       </c>
       <c r="F73">
-        <v>2470.219963976215</v>
+        <v>2505.011794454753</v>
       </c>
       <c r="G73">
         <v>115.9</v>
@@ -7279,28 +7279,28 @@
         <v>459.8</v>
       </c>
       <c r="M73">
-        <v>177.6088154098898</v>
+        <v>180.1103480212968</v>
       </c>
       <c r="N73">
-        <v>282.1911845901102</v>
+        <v>279.6896519787032</v>
       </c>
       <c r="O73">
-        <v>70.54779614752755</v>
+        <v>69.92241299467581</v>
       </c>
       <c r="P73">
-        <v>211.6433884425826</v>
+        <v>209.7672389840274</v>
       </c>
       <c r="Q73">
-        <v>388.8433884425826</v>
+        <v>386.9672389840274</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2006337226174039</v>
+        <v>0.2056760713782833</v>
       </c>
       <c r="T73">
-        <v>2.395228445866661</v>
+        <v>2.473231977538394</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.588835463706364</v>
+        <v>2.55287941559933</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09641529998591934</v>
+        <v>0.09636007041279152</v>
       </c>
       <c r="C74">
-        <v>1011.749014541329</v>
+        <v>980.6721332156399</v>
       </c>
       <c r="D74">
-        <v>3400.860808996082</v>
+        <v>3404.575758148931</v>
       </c>
       <c r="E74">
-        <v>559.4287466009293</v>
+        <v>594.2205770794674</v>
       </c>
       <c r="F74">
-        <v>2505.011794454753</v>
+        <v>2539.803624933291</v>
       </c>
       <c r="G74">
         <v>115.9</v>
@@ -7361,28 +7361,28 @@
         <v>459.8</v>
       </c>
       <c r="M74">
-        <v>180.1103480212968</v>
+        <v>182.6118806327036</v>
       </c>
       <c r="N74">
-        <v>279.6896519787032</v>
+        <v>277.1881193672964</v>
       </c>
       <c r="O74">
-        <v>69.92241299467581</v>
+        <v>69.2970298418241</v>
       </c>
       <c r="P74">
-        <v>209.7672389840274</v>
+        <v>207.8910895254723</v>
       </c>
       <c r="Q74">
-        <v>386.9672389840274</v>
+        <v>385.0910895254723</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2056760713782833</v>
+        <v>0.2110919274547834</v>
       </c>
       <c r="T74">
-        <v>2.473231977538394</v>
+        <v>2.557013548593217</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.55287941559933</v>
+        <v>2.517908464700709</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09636007041279152</v>
+        <v>0.09846934083966372</v>
       </c>
       <c r="C75">
-        <v>980.6721332156399</v>
+        <v>809.5358782915691</v>
       </c>
       <c r="D75">
-        <v>3404.575758148931</v>
+        <v>3268.231333703399</v>
       </c>
       <c r="E75">
-        <v>594.2205770794674</v>
+        <v>629.0124075580059</v>
       </c>
       <c r="F75">
-        <v>2539.803624933291</v>
+        <v>2574.59545541183</v>
       </c>
       <c r="G75">
         <v>115.9</v>
@@ -7443,45 +7443,45 @@
         <v>459.8</v>
       </c>
       <c r="M75">
-        <v>182.6118806327036</v>
+        <v>195.1543355202167</v>
       </c>
       <c r="N75">
-        <v>277.1881193672964</v>
+        <v>264.6456644797833</v>
       </c>
       <c r="O75">
-        <v>69.2970298418241</v>
+        <v>66.16141611994583</v>
       </c>
       <c r="P75">
-        <v>207.8910895254723</v>
+        <v>198.4842483598375</v>
       </c>
       <c r="Q75">
-        <v>385.0910895254723</v>
+        <v>375.6842483598375</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2110919274547834</v>
+        <v>0.2169243878448605</v>
       </c>
       <c r="T75">
-        <v>2.557013548593217</v>
+        <v>2.647239855883027</v>
       </c>
       <c r="U75">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.517908464700709</v>
+        <v>2.356083961826037</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09846934083966372</v>
+        <v>0.09844336126653593</v>
       </c>
       <c r="C76">
-        <v>809.5358782915691</v>
+        <v>776.3569245915974</v>
       </c>
       <c r="D76">
-        <v>3268.231333703399</v>
+        <v>3269.844210481965</v>
       </c>
       <c r="E76">
-        <v>629.0124075580059</v>
+        <v>663.8042380365439</v>
       </c>
       <c r="F76">
-        <v>2574.59545541183</v>
+        <v>2609.387285890368</v>
       </c>
       <c r="G76">
         <v>115.9</v>
@@ -7525,28 +7525,28 @@
         <v>459.8</v>
       </c>
       <c r="M76">
-        <v>195.1543355202167</v>
+        <v>197.7915562704899</v>
       </c>
       <c r="N76">
-        <v>264.6456644797833</v>
+        <v>262.0084437295101</v>
       </c>
       <c r="O76">
-        <v>66.16141611994583</v>
+        <v>65.50211093237752</v>
       </c>
       <c r="P76">
-        <v>198.4842483598375</v>
+        <v>196.5063327971326</v>
       </c>
       <c r="Q76">
-        <v>375.6842483598375</v>
+        <v>373.7063327971325</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2169243878448605</v>
+        <v>0.2232234450661437</v>
       </c>
       <c r="T76">
-        <v>2.647239855883027</v>
+        <v>2.744684267756022</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.356083961826037</v>
+        <v>2.324669509001691</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09844336126653593</v>
+        <v>0.09841738169340812</v>
       </c>
       <c r="C77">
-        <v>776.3569245915974</v>
+        <v>743.1795635915619</v>
       </c>
       <c r="D77">
-        <v>3269.844210481965</v>
+        <v>3271.458679960468</v>
       </c>
       <c r="E77">
-        <v>663.8042380365439</v>
+        <v>698.5960685150824</v>
       </c>
       <c r="F77">
-        <v>2609.387285890368</v>
+        <v>2644.179116368906</v>
       </c>
       <c r="G77">
         <v>115.9</v>
@@ -7607,28 +7607,28 @@
         <v>459.8</v>
       </c>
       <c r="M77">
-        <v>197.7915562704899</v>
+        <v>200.4287770207631</v>
       </c>
       <c r="N77">
-        <v>262.0084437295101</v>
+        <v>259.3712229792369</v>
       </c>
       <c r="O77">
-        <v>65.50211093237752</v>
+        <v>64.84280574480923</v>
       </c>
       <c r="P77">
-        <v>196.5063327971326</v>
+        <v>194.5284172344277</v>
       </c>
       <c r="Q77">
-        <v>373.7063327971325</v>
+        <v>371.7284172344276</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2232234450661437</v>
+        <v>0.2300474237225338</v>
       </c>
       <c r="T77">
-        <v>2.744684267756022</v>
+        <v>2.8502490472851</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.324669509001691</v>
+        <v>2.2940817523043</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09841738169340812</v>
+        <v>0.09839140212028033</v>
       </c>
       <c r="C78">
-        <v>743.1795635915619</v>
+        <v>710.0037976517897</v>
       </c>
       <c r="D78">
-        <v>3271.458679960468</v>
+        <v>3273.074744499234</v>
       </c>
       <c r="E78">
-        <v>698.5960685150824</v>
+        <v>733.3878989936209</v>
       </c>
       <c r="F78">
-        <v>2644.179116368906</v>
+        <v>2678.970946847445</v>
       </c>
       <c r="G78">
         <v>115.9</v>
@@ -7689,28 +7689,28 @@
         <v>459.8</v>
       </c>
       <c r="M78">
-        <v>200.4287770207631</v>
+        <v>203.0659977710363</v>
       </c>
       <c r="N78">
-        <v>259.3712229792369</v>
+        <v>256.7340022289637</v>
       </c>
       <c r="O78">
-        <v>64.84280574480923</v>
+        <v>64.18350055724092</v>
       </c>
       <c r="P78">
-        <v>194.5284172344277</v>
+        <v>192.5505016717228</v>
       </c>
       <c r="Q78">
-        <v>371.7284172344276</v>
+        <v>369.7505016717228</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2300474237225338</v>
+        <v>0.2374647918273057</v>
       </c>
       <c r="T78">
-        <v>2.8502490472851</v>
+        <v>2.964993372860185</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.2940817523043</v>
+        <v>2.264288482793854</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09839140212028033</v>
+        <v>0.09836542254715253</v>
       </c>
       <c r="C79">
-        <v>710.0037976517897</v>
+        <v>676.8296291372776</v>
       </c>
       <c r="D79">
-        <v>3273.074744499234</v>
+        <v>3274.69240646326</v>
       </c>
       <c r="E79">
-        <v>733.3878989936209</v>
+        <v>768.1797294721589</v>
       </c>
       <c r="F79">
-        <v>2678.970946847445</v>
+        <v>2713.762777325983</v>
       </c>
       <c r="G79">
         <v>115.9</v>
@@ -7771,28 +7771,28 @@
         <v>459.8</v>
       </c>
       <c r="M79">
-        <v>203.0659977710363</v>
+        <v>205.7032185213095</v>
       </c>
       <c r="N79">
-        <v>256.7340022289637</v>
+        <v>254.0967814786905</v>
       </c>
       <c r="O79">
-        <v>64.18350055724092</v>
+        <v>63.52419536967263</v>
       </c>
       <c r="P79">
-        <v>192.5505016717228</v>
+        <v>190.5725861090179</v>
       </c>
       <c r="Q79">
-        <v>369.7505016717228</v>
+        <v>367.7725861090179</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2374647918273057</v>
+        <v>0.2455564661234205</v>
       </c>
       <c r="T79">
-        <v>2.964993372860185</v>
+        <v>3.090169000760277</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.264288482793854</v>
+        <v>2.235259143270856</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09836542254715253</v>
+        <v>0.09833944297402472</v>
       </c>
       <c r="C80">
-        <v>676.8296291372776</v>
+        <v>643.6570604176973</v>
       </c>
       <c r="D80">
-        <v>3274.69240646326</v>
+        <v>3276.311668222218</v>
       </c>
       <c r="E80">
-        <v>768.1797294721589</v>
+        <v>802.9715599506974</v>
       </c>
       <c r="F80">
-        <v>2713.762777325983</v>
+        <v>2748.554607804521</v>
       </c>
       <c r="G80">
         <v>115.9</v>
@@ -7853,28 +7853,28 @@
         <v>459.8</v>
       </c>
       <c r="M80">
-        <v>205.7032185213095</v>
+        <v>208.3404392715827</v>
       </c>
       <c r="N80">
-        <v>254.0967814786905</v>
+        <v>251.4595607284173</v>
       </c>
       <c r="O80">
-        <v>63.52419536967263</v>
+        <v>62.86489018210432</v>
       </c>
       <c r="P80">
-        <v>190.5725861090179</v>
+        <v>188.594670546313</v>
       </c>
       <c r="Q80">
-        <v>367.7725861090179</v>
+        <v>365.7946705463129</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2455564661234205</v>
+        <v>0.2544187760667844</v>
       </c>
       <c r="T80">
-        <v>3.090169000760277</v>
+        <v>3.227266117031807</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.235259143270856</v>
+        <v>2.206964723735782</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09833944297402472</v>
+        <v>0.09831346340089692</v>
       </c>
       <c r="C81">
-        <v>643.6570604176973</v>
+        <v>610.4860938674101</v>
       </c>
       <c r="D81">
-        <v>3276.311668222218</v>
+        <v>3277.932532150469</v>
       </c>
       <c r="E81">
-        <v>802.9715599506974</v>
+        <v>837.7633904292354</v>
       </c>
       <c r="F81">
-        <v>2748.554607804521</v>
+        <v>2783.346438283059</v>
       </c>
       <c r="G81">
         <v>115.9</v>
@@ -7935,28 +7935,28 @@
         <v>459.8</v>
       </c>
       <c r="M81">
-        <v>208.3404392715827</v>
+        <v>210.9776600218559</v>
       </c>
       <c r="N81">
-        <v>251.4595607284173</v>
+        <v>248.8223399781441</v>
       </c>
       <c r="O81">
-        <v>62.86489018210432</v>
+        <v>62.20558499453603</v>
       </c>
       <c r="P81">
-        <v>188.594670546313</v>
+        <v>186.6167549836081</v>
       </c>
       <c r="Q81">
-        <v>365.7946705463129</v>
+        <v>363.8167549836081</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2544187760667844</v>
+        <v>0.2641673170044846</v>
       </c>
       <c r="T81">
-        <v>3.227266117031807</v>
+        <v>3.37807294493049</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.206964723735782</v>
+        <v>2.179377664689085</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09831346340089692</v>
+        <v>0.09828748382776911</v>
       </c>
       <c r="C82">
-        <v>610.4860938674101</v>
+        <v>577.3167318654791</v>
       </c>
       <c r="D82">
-        <v>3277.932532150469</v>
+        <v>3279.555000627077</v>
       </c>
       <c r="E82">
-        <v>837.7633904292354</v>
+        <v>872.5552209077739</v>
       </c>
       <c r="F82">
-        <v>2783.346438283059</v>
+        <v>2818.138268761598</v>
       </c>
       <c r="G82">
         <v>115.9</v>
@@ -8017,28 +8017,28 @@
         <v>459.8</v>
       </c>
       <c r="M82">
-        <v>210.9776600218559</v>
+        <v>213.6148807721291</v>
       </c>
       <c r="N82">
-        <v>248.8223399781441</v>
+        <v>246.1851192278709</v>
       </c>
       <c r="O82">
-        <v>62.20558499453603</v>
+        <v>61.54627980696772</v>
       </c>
       <c r="P82">
-        <v>186.6167549836081</v>
+        <v>184.6388394209031</v>
       </c>
       <c r="Q82">
-        <v>363.8167549836081</v>
+        <v>361.8388394209031</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2641673170044846</v>
+        <v>0.2749420201461533</v>
       </c>
       <c r="T82">
-        <v>3.37807294493049</v>
+        <v>3.544754175765876</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.179377664689085</v>
+        <v>2.152471767594157</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09828748382776911</v>
+        <v>0.09826150425464131</v>
       </c>
       <c r="C83">
-        <v>577.3167318654791</v>
+        <v>544.1489767956809</v>
       </c>
       <c r="D83">
-        <v>3279.555000627077</v>
+        <v>3281.179076035817</v>
       </c>
       <c r="E83">
-        <v>872.5552209077739</v>
+        <v>907.3470513863119</v>
       </c>
       <c r="F83">
-        <v>2818.138268761598</v>
+        <v>2852.930099240136</v>
       </c>
       <c r="G83">
         <v>115.9</v>
@@ -8099,28 +8099,28 @@
         <v>459.8</v>
       </c>
       <c r="M83">
-        <v>213.6148807721291</v>
+        <v>216.2521015224023</v>
       </c>
       <c r="N83">
-        <v>246.1851192278709</v>
+        <v>243.5478984775977</v>
       </c>
       <c r="O83">
-        <v>61.54627980696772</v>
+        <v>60.88697461939942</v>
       </c>
       <c r="P83">
-        <v>184.6388394209031</v>
+        <v>182.6609238581983</v>
       </c>
       <c r="Q83">
-        <v>361.8388394209031</v>
+        <v>359.8609238581982</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2749420201461533</v>
+        <v>0.2869139125257851</v>
       </c>
       <c r="T83">
-        <v>3.544754175765876</v>
+        <v>3.729955543360749</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.152471767594157</v>
+        <v>2.12622211189179</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09826150425464131</v>
+        <v>0.0982355246815135</v>
       </c>
       <c r="C84">
-        <v>544.1489767956809</v>
+        <v>510.9828310465136</v>
       </c>
       <c r="D84">
-        <v>3281.179076035817</v>
+        <v>3282.804760765188</v>
       </c>
       <c r="E84">
-        <v>907.3470513863119</v>
+        <v>942.1388818648504</v>
       </c>
       <c r="F84">
-        <v>2852.930099240136</v>
+        <v>2887.721929718674</v>
       </c>
       <c r="G84">
         <v>115.9</v>
@@ -8181,28 +8181,28 @@
         <v>459.8</v>
       </c>
       <c r="M84">
-        <v>216.2521015224023</v>
+        <v>218.8893222726755</v>
       </c>
       <c r="N84">
-        <v>243.5478984775977</v>
+        <v>240.9106777273245</v>
       </c>
       <c r="O84">
-        <v>60.88697461939942</v>
+        <v>60.22766943183112</v>
       </c>
       <c r="P84">
-        <v>182.6609238581983</v>
+        <v>180.6830082954934</v>
       </c>
       <c r="Q84">
-        <v>359.8609238581982</v>
+        <v>357.8830082954934</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2869139125257851</v>
+        <v>0.3002942628324325</v>
       </c>
       <c r="T84">
-        <v>3.729955543360749</v>
+        <v>3.936945307143255</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.12622211189179</v>
+        <v>2.100604978013576</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0982355246815135</v>
+        <v>0.09820954510838571</v>
       </c>
       <c r="C85">
-        <v>510.9828310465136</v>
+        <v>477.8182970112125</v>
       </c>
       <c r="D85">
-        <v>3282.804760765188</v>
+        <v>3284.432057208425</v>
       </c>
       <c r="E85">
-        <v>942.1388818648504</v>
+        <v>976.9307123433884</v>
       </c>
       <c r="F85">
-        <v>2887.721929718674</v>
+        <v>2922.513760197212</v>
       </c>
       <c r="G85">
         <v>115.9</v>
@@ -8263,28 +8263,28 @@
         <v>459.8</v>
       </c>
       <c r="M85">
-        <v>218.8893222726755</v>
+        <v>221.5265430229487</v>
       </c>
       <c r="N85">
-        <v>240.9106777273245</v>
+        <v>238.2734569770513</v>
       </c>
       <c r="O85">
-        <v>60.22766943183112</v>
+        <v>59.56836424426282</v>
       </c>
       <c r="P85">
-        <v>180.6830082954934</v>
+        <v>178.7050927327885</v>
       </c>
       <c r="Q85">
-        <v>357.8830082954934</v>
+        <v>355.9050927327885</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3002942628324325</v>
+        <v>0.3153471569274108</v>
       </c>
       <c r="T85">
-        <v>3.936945307143255</v>
+        <v>4.169808791398575</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.100604978013576</v>
+        <v>2.075597775894367</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0982095451083857</v>
+        <v>0.09818356553525791</v>
       </c>
       <c r="C86">
-        <v>477.8182970112143</v>
+        <v>444.6553770877631</v>
       </c>
       <c r="D86">
-        <v>3284.432057208426</v>
+        <v>3286.060967763513</v>
       </c>
       <c r="E86">
-        <v>976.930712343388</v>
+        <v>1011.722542821926</v>
       </c>
       <c r="F86">
-        <v>2922.513760197212</v>
+        <v>2957.30559067575</v>
       </c>
       <c r="G86">
         <v>115.9</v>
@@ -8345,28 +8345,28 @@
         <v>459.8</v>
       </c>
       <c r="M86">
-        <v>221.5265430229487</v>
+        <v>224.1637637732219</v>
       </c>
       <c r="N86">
-        <v>238.2734569770513</v>
+        <v>235.6362362267781</v>
       </c>
       <c r="O86">
-        <v>59.56836424426283</v>
+        <v>58.90905905669453</v>
       </c>
       <c r="P86">
-        <v>178.7050927327885</v>
+        <v>176.7271771700836</v>
       </c>
       <c r="Q86">
-        <v>355.9050927327885</v>
+        <v>353.9271771700836</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3153471569274106</v>
+        <v>0.332407103568386</v>
       </c>
       <c r="T86">
-        <v>4.169808791398571</v>
+        <v>4.433720740221267</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.075597775894367</v>
+        <v>2.051178978530904</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09818356553525791</v>
+        <v>0.09815758596213009</v>
       </c>
       <c r="C87">
-        <v>444.6553770877631</v>
+        <v>411.4940736789076</v>
       </c>
       <c r="D87">
-        <v>3286.060967763513</v>
+        <v>3287.691494833196</v>
       </c>
       <c r="E87">
-        <v>1011.722542821926</v>
+        <v>1046.514373300465</v>
       </c>
       <c r="F87">
-        <v>2957.30559067575</v>
+        <v>2992.097421154288</v>
       </c>
       <c r="G87">
         <v>115.9</v>
@@ -8427,28 +8427,28 @@
         <v>459.8</v>
       </c>
       <c r="M87">
-        <v>224.1637637732219</v>
+        <v>226.8009845234951</v>
       </c>
       <c r="N87">
-        <v>235.6362362267781</v>
+        <v>232.9990154765049</v>
       </c>
       <c r="O87">
-        <v>58.90905905669453</v>
+        <v>58.24975386912623</v>
       </c>
       <c r="P87">
-        <v>176.7271771700836</v>
+        <v>174.7492616073787</v>
       </c>
       <c r="Q87">
-        <v>353.9271771700836</v>
+        <v>351.9492616073787</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.332407103568386</v>
+        <v>0.3519041854437863</v>
       </c>
       <c r="T87">
-        <v>4.433720740221267</v>
+        <v>4.735334396018631</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.051178978530904</v>
+        <v>2.027328060175893</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09815758596213009</v>
+        <v>0.09813160638900228</v>
       </c>
       <c r="C88">
-        <v>411.4940736789076</v>
+        <v>378.3343891921577</v>
       </c>
       <c r="D88">
-        <v>3287.691494833196</v>
+        <v>3289.323640824985</v>
       </c>
       <c r="E88">
-        <v>1046.514373300465</v>
+        <v>1081.306203779003</v>
       </c>
       <c r="F88">
-        <v>2992.097421154288</v>
+        <v>3026.889251632827</v>
       </c>
       <c r="G88">
         <v>115.9</v>
@@ -8509,28 +8509,28 @@
         <v>459.8</v>
       </c>
       <c r="M88">
-        <v>226.8009845234951</v>
+        <v>229.4382052737683</v>
       </c>
       <c r="N88">
-        <v>232.9990154765049</v>
+        <v>230.3617947262317</v>
       </c>
       <c r="O88">
-        <v>58.24975386912623</v>
+        <v>57.59044868155793</v>
       </c>
       <c r="P88">
-        <v>174.7492616073787</v>
+        <v>172.7713460446738</v>
       </c>
       <c r="Q88">
-        <v>351.9492616073787</v>
+        <v>349.9713460446738</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3519041854437863</v>
+        <v>0.3744008183769406</v>
       </c>
       <c r="T88">
-        <v>4.735334396018631</v>
+        <v>5.083350152707898</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.027328060175893</v>
+        <v>2.004025438794561</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09813160638900228</v>
+        <v>0.1074776268158745</v>
       </c>
       <c r="C89">
-        <v>378.3343891921577</v>
+        <v>-154.8891664485359</v>
       </c>
       <c r="D89">
-        <v>3289.323640824985</v>
+        <v>2790.891915662829</v>
       </c>
       <c r="E89">
-        <v>1081.306203779003</v>
+        <v>1116.098034257541</v>
       </c>
       <c r="F89">
-        <v>3026.889251632827</v>
+        <v>3061.681082111365</v>
       </c>
       <c r="G89">
         <v>115.9</v>
@@ -8591,45 +8591,45 @@
         <v>459.8</v>
       </c>
       <c r="M89">
-        <v>229.4382052737683</v>
+        <v>275.5512973900229</v>
       </c>
       <c r="N89">
-        <v>230.3617947262317</v>
+        <v>184.2487026099772</v>
       </c>
       <c r="O89">
-        <v>57.59044868155793</v>
+        <v>46.06217565249429</v>
       </c>
       <c r="P89">
-        <v>172.7713460446738</v>
+        <v>138.1865269574829</v>
       </c>
       <c r="Q89">
-        <v>349.9713460446738</v>
+        <v>315.3865269574828</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3744008183769406</v>
+        <v>0.4006468901322874</v>
       </c>
       <c r="T89">
-        <v>5.083350152707898</v>
+        <v>5.489368535512044</v>
       </c>
       <c r="U89">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V89">
         <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.004025438794561</v>
+        <v>1.668654818014471</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1074776268158745</v>
+        <v>0.1075581472427467</v>
       </c>
       <c r="C90">
-        <v>-154.8891664485359</v>
+        <v>-193.3197687885422</v>
       </c>
       <c r="D90">
-        <v>2790.891915662829</v>
+        <v>2787.253143801361</v>
       </c>
       <c r="E90">
-        <v>1116.098034257541</v>
+        <v>1150.88986473608</v>
       </c>
       <c r="F90">
-        <v>3061.681082111365</v>
+        <v>3096.472912589903</v>
       </c>
       <c r="G90">
         <v>115.9</v>
@@ -8673,28 +8673,28 @@
         <v>459.8</v>
       </c>
       <c r="M90">
-        <v>275.5512973900229</v>
+        <v>278.6825621330913</v>
       </c>
       <c r="N90">
-        <v>184.2487026099772</v>
+        <v>181.1174378669087</v>
       </c>
       <c r="O90">
-        <v>46.06217565249429</v>
+        <v>45.27935946672717</v>
       </c>
       <c r="P90">
-        <v>138.1865269574829</v>
+        <v>135.8380784001815</v>
       </c>
       <c r="Q90">
-        <v>315.3865269574828</v>
+        <v>313.0380784001815</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4006468901322874</v>
+        <v>0.4316649749340608</v>
       </c>
       <c r="T90">
-        <v>5.489368535512044</v>
+        <v>5.969208442462398</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.668654818014471</v>
+        <v>1.649905887474983</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1075581472427467</v>
+        <v>0.1076386676696189</v>
       </c>
       <c r="C91">
-        <v>-193.3197687885422</v>
+        <v>-231.740895003833</v>
       </c>
       <c r="D91">
-        <v>2787.253143801361</v>
+        <v>2783.623848064609</v>
       </c>
       <c r="E91">
-        <v>1150.88986473608</v>
+        <v>1185.681695214618</v>
       </c>
       <c r="F91">
-        <v>3096.472912589903</v>
+        <v>3131.264743068442</v>
       </c>
       <c r="G91">
         <v>115.9</v>
@@ -8755,28 +8755,28 @@
         <v>459.8</v>
       </c>
       <c r="M91">
-        <v>278.6825621330913</v>
+        <v>281.8138268761597</v>
       </c>
       <c r="N91">
-        <v>181.1174378669087</v>
+        <v>177.9861731238403</v>
       </c>
       <c r="O91">
-        <v>45.27935946672717</v>
+        <v>44.49654328096007</v>
       </c>
       <c r="P91">
-        <v>135.8380784001815</v>
+        <v>133.4896298428802</v>
       </c>
       <c r="Q91">
-        <v>313.0380784001815</v>
+        <v>310.6896298428802</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4316649749340608</v>
+        <v>0.4688866766961889</v>
       </c>
       <c r="T91">
-        <v>5.969208442462398</v>
+        <v>6.545016330802824</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.649905887474983</v>
+        <v>1.631573599836372</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1076386676696189</v>
+        <v>0.1077191880964911</v>
       </c>
       <c r="C92">
-        <v>-231.740895003833</v>
+        <v>-270.1525820629922</v>
       </c>
       <c r="D92">
-        <v>2783.623848064609</v>
+        <v>2780.003991483988</v>
       </c>
       <c r="E92">
-        <v>1185.681695214618</v>
+        <v>1220.473525693156</v>
       </c>
       <c r="F92">
-        <v>3131.264743068442</v>
+        <v>3166.05657354698</v>
       </c>
       <c r="G92">
         <v>115.9</v>
@@ -8837,28 +8837,28 @@
         <v>459.8</v>
       </c>
       <c r="M92">
-        <v>281.8138268761597</v>
+        <v>284.9450916192282</v>
       </c>
       <c r="N92">
-        <v>177.9861731238403</v>
+        <v>174.8549083807718</v>
       </c>
       <c r="O92">
-        <v>44.49654328096007</v>
+        <v>43.71372709519295</v>
       </c>
       <c r="P92">
-        <v>133.4896298428802</v>
+        <v>131.1411812855789</v>
       </c>
       <c r="Q92">
-        <v>310.6896298428802</v>
+        <v>308.3411812855788</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4688866766961889</v>
+        <v>0.5143798677387899</v>
       </c>
       <c r="T92">
-        <v>6.545016330802824</v>
+        <v>7.248781527663342</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.631573599836372</v>
+        <v>1.61364421961839</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1077191880964911</v>
+        <v>0.1077997085233633</v>
       </c>
       <c r="C93">
-        <v>-270.1525820629922</v>
+        <v>-308.5548667425587</v>
       </c>
       <c r="D93">
-        <v>2780.003991483988</v>
+        <v>2776.39353728296</v>
       </c>
       <c r="E93">
-        <v>1220.473525693156</v>
+        <v>1255.265356171695</v>
       </c>
       <c r="F93">
-        <v>3166.05657354698</v>
+        <v>3200.848404025518</v>
       </c>
       <c r="G93">
         <v>115.9</v>
@@ -8919,28 +8919,28 @@
         <v>459.8</v>
       </c>
       <c r="M93">
-        <v>284.9450916192282</v>
+        <v>288.0763563622966</v>
       </c>
       <c r="N93">
-        <v>174.8549083807718</v>
+        <v>171.7236436377034</v>
       </c>
       <c r="O93">
-        <v>43.71372709519295</v>
+        <v>42.93091090942585</v>
       </c>
       <c r="P93">
-        <v>131.1411812855789</v>
+        <v>128.7927327282775</v>
       </c>
       <c r="Q93">
-        <v>308.3411812855788</v>
+        <v>305.9927327282775</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5143798677387899</v>
+        <v>0.5712463565420411</v>
       </c>
       <c r="T93">
-        <v>7.248781527663342</v>
+        <v>8.128488023738994</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.61364421961839</v>
+        <v>1.596104608535581</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1077997085233633</v>
+        <v>0.1078802289502355</v>
       </c>
       <c r="C94">
-        <v>-308.5548667425587</v>
+        <v>-346.9477856282683</v>
       </c>
       <c r="D94">
-        <v>2776.39353728296</v>
+        <v>2772.792448875788</v>
       </c>
       <c r="E94">
-        <v>1255.265356171695</v>
+        <v>1290.057186650233</v>
       </c>
       <c r="F94">
-        <v>3200.848404025518</v>
+        <v>3235.640234504056</v>
       </c>
       <c r="G94">
         <v>115.9</v>
@@ -9001,28 +9001,28 @@
         <v>459.8</v>
       </c>
       <c r="M94">
-        <v>288.0763563622966</v>
+        <v>291.2076211053651</v>
       </c>
       <c r="N94">
-        <v>171.7236436377034</v>
+        <v>168.5923788946349</v>
       </c>
       <c r="O94">
-        <v>42.93091090942585</v>
+        <v>42.14809472365873</v>
       </c>
       <c r="P94">
-        <v>128.7927327282775</v>
+        <v>126.4442841709762</v>
       </c>
       <c r="Q94">
-        <v>305.9927327282775</v>
+        <v>303.6442841709762</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5712463565420411</v>
+        <v>0.6443604135747929</v>
       </c>
       <c r="T94">
-        <v>8.128488023738994</v>
+        <v>9.259539232979115</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.596104608535581</v>
+        <v>1.578942193390037</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1078802289502355</v>
+        <v>0.1079607493771077</v>
       </c>
       <c r="C95">
-        <v>-346.9477856282683</v>
+        <v>-385.33137511629</v>
       </c>
       <c r="D95">
-        <v>2772.792448875788</v>
+        <v>2769.200689866305</v>
       </c>
       <c r="E95">
-        <v>1290.057186650233</v>
+        <v>1324.849017128771</v>
       </c>
       <c r="F95">
-        <v>3235.640234504056</v>
+        <v>3270.432064982595</v>
       </c>
       <c r="G95">
         <v>115.9</v>
@@ -9083,28 +9083,28 @@
         <v>459.8</v>
       </c>
       <c r="M95">
-        <v>291.2076211053651</v>
+        <v>294.3388858484336</v>
       </c>
       <c r="N95">
-        <v>168.5923788946349</v>
+        <v>165.4611141515664</v>
       </c>
       <c r="O95">
-        <v>42.14809472365873</v>
+        <v>41.36527853789161</v>
       </c>
       <c r="P95">
-        <v>126.4442841709762</v>
+        <v>124.0958356136748</v>
       </c>
       <c r="Q95">
-        <v>303.6442841709762</v>
+        <v>301.2958356136749</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6443604135747929</v>
+        <v>0.741845822951795</v>
       </c>
       <c r="T95">
-        <v>9.259539232979115</v>
+        <v>10.76760751196594</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.578942193390037</v>
+        <v>1.562144936013547</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1079607493771077</v>
+        <v>0.1080412698039799</v>
       </c>
       <c r="C96">
-        <v>-385.33137511629</v>
+        <v>-423.7056714144537</v>
       </c>
       <c r="D96">
-        <v>2769.200689866305</v>
+        <v>2765.618224046679</v>
       </c>
       <c r="E96">
-        <v>1324.849017128771</v>
+        <v>1359.640847607309</v>
       </c>
       <c r="F96">
-        <v>3270.432064982595</v>
+        <v>3305.223895461133</v>
       </c>
       <c r="G96">
         <v>115.9</v>
@@ -9165,28 +9165,28 @@
         <v>459.8</v>
       </c>
       <c r="M96">
-        <v>294.3388858484336</v>
+        <v>297.470150591502</v>
       </c>
       <c r="N96">
-        <v>165.4611141515664</v>
+        <v>162.329849408498</v>
       </c>
       <c r="O96">
-        <v>41.36527853789161</v>
+        <v>40.58246235212451</v>
       </c>
       <c r="P96">
-        <v>124.0958356136748</v>
+        <v>121.7473870563735</v>
       </c>
       <c r="Q96">
-        <v>301.2958356136749</v>
+        <v>298.9473870563735</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.741845822951795</v>
+        <v>0.8783253960795985</v>
       </c>
       <c r="T96">
-        <v>10.76760751196594</v>
+        <v>12.87890310254751</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.562144936013547</v>
+        <v>1.545701305108142</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1080412698039799</v>
+        <v>0.1081217902308521</v>
       </c>
       <c r="C97">
-        <v>-423.7056714144537</v>
+        <v>-462.0707105434635</v>
       </c>
       <c r="D97">
-        <v>2765.618224046679</v>
+        <v>2762.045015396208</v>
       </c>
       <c r="E97">
-        <v>1359.640847607309</v>
+        <v>1394.432678085848</v>
       </c>
       <c r="F97">
-        <v>3305.223895461133</v>
+        <v>3340.015725939671</v>
       </c>
       <c r="G97">
         <v>115.9</v>
@@ -9247,28 +9247,28 @@
         <v>459.8</v>
       </c>
       <c r="M97">
-        <v>297.470150591502</v>
+        <v>300.6014153345704</v>
       </c>
       <c r="N97">
-        <v>162.329849408498</v>
+        <v>159.1985846654296</v>
       </c>
       <c r="O97">
-        <v>40.58246235212451</v>
+        <v>39.79964616635739</v>
       </c>
       <c r="P97">
-        <v>121.7473870563735</v>
+        <v>119.3989384990722</v>
       </c>
       <c r="Q97">
-        <v>298.9473870563735</v>
+        <v>296.5989384990722</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8783253960795985</v>
+        <v>1.083044755771303</v>
       </c>
       <c r="T97">
-        <v>12.87890310254751</v>
+        <v>16.04584648841985</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.545701305108142</v>
+        <v>1.529600249846598</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1081217902308521</v>
+        <v>0.1082023106577243</v>
       </c>
       <c r="C98">
-        <v>-462.0707105434631</v>
+        <v>-500.4265283381087</v>
       </c>
       <c r="D98">
-        <v>2762.045015396208</v>
+        <v>2758.4810280801</v>
       </c>
       <c r="E98">
-        <v>1394.432678085847</v>
+        <v>1429.224508564385</v>
       </c>
       <c r="F98">
-        <v>3340.015725939671</v>
+        <v>3374.807556418209</v>
       </c>
       <c r="G98">
         <v>115.9</v>
@@ -9329,28 +9329,28 @@
         <v>459.8</v>
       </c>
       <c r="M98">
-        <v>300.6014153345704</v>
+        <v>303.7326800776388</v>
       </c>
       <c r="N98">
-        <v>159.1985846654296</v>
+        <v>156.0673199223612</v>
       </c>
       <c r="O98">
-        <v>39.79964616635741</v>
+        <v>39.0168299805903</v>
       </c>
       <c r="P98">
-        <v>119.3989384990722</v>
+        <v>117.0504899417709</v>
       </c>
       <c r="Q98">
-        <v>296.5989384990722</v>
+        <v>294.2504899417709</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.083044755771301</v>
+        <v>1.424243688590808</v>
       </c>
       <c r="T98">
-        <v>16.04584648841981</v>
+        <v>21.32408546487369</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.529600249846599</v>
+        <v>1.513831175105912</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1082023106577243</v>
+        <v>0.1540458194790851</v>
       </c>
       <c r="C99">
-        <v>-500.4265283381087</v>
+        <v>-1703.470859956245</v>
       </c>
       <c r="D99">
-        <v>2758.4810280801</v>
+        <v>1590.228526940502</v>
       </c>
       <c r="E99">
-        <v>1429.224508564385</v>
+        <v>1464.016339042924</v>
       </c>
       <c r="F99">
-        <v>3374.807556418209</v>
+        <v>3409.599386896748</v>
       </c>
       <c r="G99">
         <v>115.9</v>
@@ -9411,45 +9411,45 @@
         <v>459.8</v>
       </c>
       <c r="M99">
-        <v>303.7326800776388</v>
+        <v>500.5291899964426</v>
       </c>
       <c r="N99">
-        <v>156.0673199223612</v>
+        <v>-40.72918999644259</v>
       </c>
       <c r="O99">
-        <v>39.0168299805903</v>
+        <v>-10.18229749911065</v>
       </c>
       <c r="P99">
-        <v>117.0504899417709</v>
+        <v>-30.54689249733194</v>
       </c>
       <c r="Q99">
-        <v>294.2504899417709</v>
+        <v>146.653107502668</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.424243688590808</v>
+        <v>2.161059243788578</v>
       </c>
       <c r="T99">
-        <v>21.32408546487369</v>
+        <v>32.72238776835628</v>
       </c>
       <c r="U99">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.25</v>
+        <v>0.2296569356940341</v>
       </c>
       <c r="W99">
-        <v>0.0675</v>
+        <v>0.1130863618401158</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.513831175105912</v>
+        <v>0.9186277427761365</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1540458194790851</v>
+        <v>0.1550558194790851</v>
       </c>
       <c r="C100">
-        <v>-1703.470859956245</v>
+        <v>-1752.963333566359</v>
       </c>
       <c r="D100">
-        <v>1590.228526940502</v>
+        <v>1575.527883808926</v>
       </c>
       <c r="E100">
-        <v>1464.016339042924</v>
+        <v>1498.808169521462</v>
       </c>
       <c r="F100">
-        <v>3409.599386896748</v>
+        <v>3444.391217375286</v>
       </c>
       <c r="G100">
         <v>115.9</v>
@@ -9493,37 +9493,37 @@
         <v>459.8</v>
       </c>
       <c r="M100">
-        <v>500.5291899964426</v>
+        <v>505.636630710692</v>
       </c>
       <c r="N100">
-        <v>-40.72918999644259</v>
+        <v>-45.83663071069196</v>
       </c>
       <c r="O100">
-        <v>-10.18229749911065</v>
+        <v>-11.45915767767299</v>
       </c>
       <c r="P100">
-        <v>-30.54689249733194</v>
+        <v>-34.37747303301897</v>
       </c>
       <c r="Q100">
-        <v>146.653107502668</v>
+        <v>142.822526966981</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.161059243788578</v>
+        <v>4.276318487577157</v>
       </c>
       <c r="T100">
-        <v>32.72238776835628</v>
+        <v>65.44477553671256</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2296569356940341</v>
+        <v>0.2273371686668217</v>
       </c>
       <c r="W100">
-        <v>0.1130863618401158</v>
+        <v>0.1134269036397106</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9186277427761365</v>
+        <v>0.9093486746672866</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1550558194790851</v>
-      </c>
-      <c r="C101">
-        <v>-1752.963333566359</v>
-      </c>
-      <c r="D101">
-        <v>1575.527883808926</v>
-      </c>
-      <c r="E101">
-        <v>1498.808169521462</v>
-      </c>
-      <c r="F101">
-        <v>3444.391217375286</v>
-      </c>
-      <c r="G101">
-        <v>115.9</v>
-      </c>
-      <c r="H101">
-        <v>1533.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>637</v>
-      </c>
-      <c r="K101">
-        <v>177.2</v>
-      </c>
-      <c r="L101">
-        <v>459.8</v>
-      </c>
-      <c r="M101">
-        <v>505.636630710692</v>
-      </c>
-      <c r="N101">
-        <v>-45.83663071069196</v>
-      </c>
-      <c r="O101">
-        <v>-11.45915767767299</v>
-      </c>
-      <c r="P101">
-        <v>-34.37747303301897</v>
-      </c>
-      <c r="Q101">
-        <v>142.822526966981</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.276318487577157</v>
-      </c>
-      <c r="T101">
-        <v>65.44477553671256</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2273371686668217</v>
-      </c>
-      <c r="W101">
-        <v>0.1134269036397106</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9093486746672866</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
